--- a/outputs/Model_Sensitivity_Audit_v27.xlsx
+++ b/outputs/Model_Sensitivity_Audit_v27.xlsx
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -643,10 +643,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.526479999999951</v>
+        <v>4.52647999999995</v>
       </c>
       <c r="C6" t="n">
-        <v>4.666221474017745</v>
+        <v>4.666221474017744</v>
       </c>
       <c r="D6" t="n">
         <v>2.919999999999996</v>
@@ -955,7 +955,7 @@
         <v>2.919999999999996</v>
       </c>
       <c r="E7" t="n">
-        <v>2.905332478545524</v>
+        <v>2.905332478545528</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -968,16 +968,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.105200000000003</v>
+        <v>6.105200000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>6.287706569606076</v>
+        <v>6.287706569606078</v>
       </c>
       <c r="D8" t="n">
         <v>2.919999999999996</v>
       </c>
       <c r="E8" t="n">
-        <v>2.928560000000143</v>
+        <v>2.928560000000144</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.5903</v>
+        <v>0.5986</v>
       </c>
       <c r="G6" t="n">
         <v>0.54</v>
@@ -1222,7 +1222,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.3817</v>
+        <v>0.3779</v>
       </c>
       <c r="G7" t="n">
         <v>0.43</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.613</v>
+        <v>0.6183333333</v>
       </c>
       <c r="G8" t="n">
         <v>0.54</v>
@@ -1286,7 +1286,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.3153333333</v>
+        <v>0.3143333333</v>
       </c>
       <c r="G9" t="n">
         <v>0.25</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.398</v>
+        <v>0.4153333333</v>
       </c>
       <c r="G18" t="n">
         <v>0.36</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5466666667</v>
       </c>
       <c r="G19" t="n">
         <v>0.33</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="n">
-        <v>-0.162</v>
+        <v>-0.1313333334</v>
       </c>
       <c r="G20" t="n">
         <v>-0.22</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.39925</v>
+        <v>0.3923333333</v>
       </c>
       <c r="G21" t="n">
         <v>0.35</v>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.55925</v>
+        <v>0.5673333333</v>
       </c>
       <c r="G22" t="n">
         <v>0.5</v>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>-0.16</v>
+        <v>-0.175</v>
       </c>
       <c r="G23" t="n">
         <v>-0.23</v>
@@ -2166,7 +2166,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.4752</v>
+        <v>0.4856</v>
       </c>
       <c r="G37" t="n">
         <v>0.413</v>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.4108</v>
+        <v>0.4148</v>
       </c>
       <c r="G38" t="n">
         <v>0.406</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G48" t="n">
         <v>136</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G53" t="n">
         <v>13</v>
@@ -2742,7 +2742,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G55" t="n">
         <v>149</v>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3397,22 +3397,22 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.3125287468049009</v>
+        <v>-0.3164969250962884</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3119064128435127</v>
+        <v>-0.3158745723692391</v>
       </c>
       <c r="I2" t="n">
         <v>-7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002291745046989035</v>
+        <v>0.04338122426284485</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002291682922951566</v>
+        <v>0.04335687850357317</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3439,19 +3439,19 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8072625851461908</v>
+        <v>-0.8062519231254157</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.803123407924403</v>
+        <v>-0.8022261050652446</v>
       </c>
       <c r="I3" t="n">
         <v>-7</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.1297488434593532</v>
+        <v>-0.1018944957458672</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1299462210230828</v>
+        <v>-0.1020272296690905</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -3481,19 +3481,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8072625851461623</v>
+        <v>-0.8062519231254157</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8031234079243461</v>
+        <v>-0.8022261050652446</v>
       </c>
       <c r="I4" t="n">
         <v>-7</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1297488434593532</v>
+        <v>-0.1018944957458672</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1299462210230828</v>
+        <v>-0.1020272296690905</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -3523,22 +3523,22 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7709419697065982</v>
+        <v>-0.7809055207092968</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7671660024290361</v>
+        <v>-0.7771282181151662</v>
       </c>
       <c r="I5" t="n">
         <v>-7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03136296700168373</v>
+        <v>0.005215323361611013</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0313513099980085</v>
+        <v>0.005214972569710596</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3567,19 +3567,19 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2940874842407482</v>
+        <v>-0.2998877054193656</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2935363632929864</v>
+        <v>-0.2993288987964888</v>
       </c>
       <c r="I6" t="n">
         <v>-7</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1009847027818296</v>
+        <v>-0.05676599178111275</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1011045008627534</v>
+        <v>-0.05680734152560518</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -3611,19 +3611,19 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2951892727470238</v>
+        <v>0.3010071094158207</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2957465697284078</v>
+        <v>0.3015722657384572</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0851530560426923</v>
+        <v>0.04904017717225884</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08506682516627251</v>
+        <v>0.04900905138711664</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -3655,22 +3655,22 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4441661702821307</v>
+        <v>0.2942565267130703</v>
       </c>
       <c r="H8" t="n">
-        <v>0.445429086056464</v>
+        <v>0.2947965950182549</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09292238545732801</v>
+        <v>0.0346087640962125</v>
       </c>
       <c r="K8" t="n">
-        <v>0.09281965028182526</v>
+        <v>0.03459327997057215</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3699,19 +3699,19 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4389562384045291</v>
+        <v>-0.4512354555604077</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4377295321019687</v>
+        <v>-0.4499715197302123</v>
       </c>
       <c r="I9" t="n">
         <v>-7</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1177790969097643</v>
+        <v>-0.05195563679904325</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.117941869358603</v>
+        <v>-0.05199028916699433</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -3743,19 +3743,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05365183128279227</v>
+        <v>0.05295180917835296</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0536702138295766</v>
+        <v>0.05296927104313909</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.007361058019938582</v>
+        <v>0.01220734939322909</v>
       </c>
       <c r="K10" t="n">
-        <v>0.007360416881226683</v>
+        <v>0.01220542641263478</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -3787,19 +3787,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.053656387507516</v>
+        <v>-0.05295632009580231</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05363801410535984</v>
+        <v>-0.05293886709461049</v>
       </c>
       <c r="I11" t="n">
         <v>-7</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.007331590091254725</v>
+        <v>-0.01218643561058741</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.007332225493328792</v>
+        <v>-0.01218834823081494</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -3831,19 +3831,19 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.05652815429124303</v>
+        <v>-0.05558641237902862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0565077618808516</v>
+        <v>-0.05556718303432717</v>
       </c>
       <c r="I12" t="n">
         <v>-7</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.01004944359385007</v>
+        <v>-0.01465292752899217</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01005063719318144</v>
+        <v>-0.01465569216039597</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05653379458084373</v>
+        <v>0.05559201482324738</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05655420540890077</v>
+        <v>0.05561126174026754</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.01007973186388256</v>
+        <v>0.01467572534150463</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01007852946970189</v>
+        <v>0.01467294551483178</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -3919,19 +3919,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3211030385550657</v>
+        <v>-0.3236011072892779</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3204461238151737</v>
+        <v>-0.3229505318565771</v>
       </c>
       <c r="I14" t="n">
         <v>-7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001173706387312734</v>
+        <v>0.01457197990528414</v>
       </c>
       <c r="K14" t="n">
-        <v>0.001173690093828839</v>
+        <v>0.01456923926483</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3963,19 +3963,19 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3213844450197314</v>
+        <v>0.3239052418136055</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3220451466042675</v>
+        <v>0.3245597485301914</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.008703078705217138</v>
+        <v>-0.01461259870571041</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.008703973985198843</v>
+        <v>-0.01461534814902876</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.05952828049066738</v>
+        <v>-0.06073184963096878</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05950566648436961</v>
+        <v>-0.06070889629160092</v>
       </c>
       <c r="I16" t="n">
         <v>-7</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03030945101534144</v>
+        <v>-0.01841087312489265</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.03032029401027359</v>
+        <v>-0.0184152363204575</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -4051,22 +4051,22 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05956087807294352</v>
+        <v>0.06076484571792662</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0595835336274888</v>
+        <v>0.06078784188747477</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0277843258733057</v>
+        <v>0.01835611953902827</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02777517945376928</v>
+        <v>0.01835176934054061</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4095,22 +4095,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3001232852066948</v>
+        <v>0.3032831367893039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3006993855562712</v>
+        <v>0.3038568804258261</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0373143050320266</v>
+        <v>0.01590352257505856</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03729779790335641</v>
+        <v>0.01590025783813331</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4139,19 +4139,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2996764387044664</v>
+        <v>-0.3028200617395953</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2991041913431332</v>
+        <v>-0.302250284258065</v>
       </c>
       <c r="I19" t="n">
         <v>-7</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.03728116709918794</v>
+        <v>-0.01591056242529021</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03729756435865994</v>
+        <v>-0.01591382165641875</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4183,19 +4183,19 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.03030244040334651</v>
+        <v>0.03248639367402006</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03030830352358294</v>
+        <v>0.03249296533556389</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.03235035162374089</v>
+        <v>-0.04610413354130571</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.03236270234643968</v>
+        <v>-0.04613143307888379</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4227,19 +4227,19 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0311305961826065</v>
+        <v>0.02949494713334389</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03113678418824861</v>
+        <v>0.02950036413685098</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.02762594874204183</v>
+        <v>0.04579953092574129</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02761690639211878</v>
+        <v>0.04577238992869326</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -4271,19 +4271,19 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3080893785780461</v>
+        <v>0.3143886150797925</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3086964971613497</v>
+        <v>0.3150051895931938</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1024436017119825</v>
+        <v>-0.07696176213567441</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1025668740167873</v>
+        <v>-0.07703764180318018</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4315,19 +4315,19 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3395127668861448</v>
+        <v>-0.3464141152232969</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3387784522788877</v>
+        <v>-0.3456686888700915</v>
       </c>
       <c r="I23" t="n">
         <v>-7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09560640009879506</v>
+        <v>0.06925516751974925</v>
       </c>
       <c r="K23" t="n">
-        <v>0.09549762563361952</v>
+        <v>0.06919299184772854</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -4359,22 +4359,22 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.07821108943522859</v>
+        <v>-0.08090782947624575</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.07817205778323455</v>
+        <v>-0.08086709728820551</v>
       </c>
       <c r="I24" t="n">
         <v>-7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04192660261848857</v>
+        <v>0.03714301269324238</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04190575625515436</v>
+        <v>0.03712517424810358</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -4403,19 +4403,19 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2332891881905255</v>
+        <v>0.2400240661790747</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2336371318401973</v>
+        <v>0.2403832828423731</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1146751935191261</v>
+        <v>-0.1021035317526398</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.1148295322542907</v>
+        <v>-0.1022368085307619</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -4447,19 +4447,19 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2356178758797114</v>
+        <v>-0.2351818581689713</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2352639848791114</v>
+        <v>-0.2348380365043852</v>
       </c>
       <c r="I26" t="n">
         <v>-7</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.05438371654697249</v>
+        <v>-0.0495461591361277</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.05441856918545795</v>
+        <v>-0.04957767819480807</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -4491,19 +4491,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2355796284258531</v>
+        <v>0.2351455795906077</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2359344428760153</v>
+        <v>0.2354903318070569</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.05448392150327663</v>
+        <v>0.04965765940750089</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0544486891933289</v>
+        <v>0.04962574328126124</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -4535,22 +4535,22 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3581325306164729</v>
+        <v>0.3606022311215611</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3589531493393281</v>
+        <v>0.3614136329102848</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01182625669306248</v>
+        <v>0.02678478518168959</v>
       </c>
       <c r="K28" t="n">
-        <v>0.01182460133026808</v>
+        <v>0.02677551649762222</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -4579,19 +4579,19 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.3579103957770258</v>
+        <v>-0.3603500399918005</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3570944367526749</v>
+        <v>-0.3595435043455666</v>
       </c>
       <c r="I29" t="n">
         <v>-7</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.01500763239558722</v>
+        <v>-0.02643741338407324</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.01501029346938054</v>
+        <v>-0.02644640443317314</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4623,19 +4623,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.04676451220777267</v>
+        <v>-0.04562149713052577</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.04675055501158454</v>
+        <v>-0.04560854342520315</v>
       </c>
       <c r="I30" t="n">
         <v>-7</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.03174444443217794</v>
+        <v>-0.02652393428321176</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.03175633731851235</v>
+        <v>-0.02653298421432737</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4667,22 +4667,22 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.04681953413410156</v>
+        <v>0.04567669565201982</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04683353233841103</v>
+        <v>0.04568968831500797</v>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03174739053383036</v>
+        <v>0.02651904954750961</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0317354457143324</v>
+        <v>0.02650996405698436</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -4711,22 +4711,22 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.03814300525644398</v>
+        <v>0.03737157211730846</v>
       </c>
       <c r="H32" t="n">
-        <v>0.03815229544571253</v>
+        <v>0.03738026909763903</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02597939118842874</v>
+        <v>0.02172950348279556</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02597139545664362</v>
+        <v>0.02172340579992493</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4755,19 +4755,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.03811703065451866</v>
+        <v>-0.0373455374044056</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.03810775751321671</v>
+        <v>-0.0373368566910699</v>
       </c>
       <c r="I33" t="n">
         <v>-7</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.02597864980319287</v>
+        <v>-0.02173431328657216</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.02598661783080303</v>
+        <v>-0.02174039226289892</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -4841,22 +4841,22 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1551532083159373</v>
+        <v>0.1575828816650358</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1553070349019663</v>
+        <v>0.1577376339638477</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
-        <v>0.04417446413326331</v>
+        <v>0.02723324340602318</v>
       </c>
       <c r="K35" t="n">
-        <v>0.0441513191484475</v>
+        <v>0.02722366140689303</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -4885,19 +4885,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.1549537729469534</v>
+        <v>-0.1573796752282135</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1548006372142652</v>
+        <v>-0.1572256327419268</v>
       </c>
       <c r="I36" t="n">
         <v>-7</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.04877035911081151</v>
+        <v>-0.02734228431333463</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04879839874392644</v>
+        <v>-0.02735190065853033</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4929,19 +4929,19 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.2732823312273922</v>
+        <v>-0.2758941196722446</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.272806367753077</v>
+        <v>-0.2754210812584006</v>
       </c>
       <c r="I37" t="n">
         <v>-7</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.06663464256588725</v>
+        <v>-0.04105548082971922</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.06668692339174243</v>
+        <v>-0.04107713776815558</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4973,19 +4973,19 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2735619936048295</v>
+        <v>0.2761827395412979</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2740405566458151</v>
+        <v>0.2766584467408393</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
-        <v>0.06291996118287813</v>
+        <v>0.04096484050377569</v>
       </c>
       <c r="K38" t="n">
-        <v>0.06287294817619937</v>
+        <v>0.04094313558092466</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -5059,22 +5059,22 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4987791696512147</v>
+        <v>0.5039084136928977</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5003722785033915</v>
+        <v>0.5054943131280538</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04471885738133352</v>
+        <v>0.005720233903936389</v>
       </c>
       <c r="K40" t="n">
-        <v>0.0446951375795237</v>
+        <v>0.005719811884588921</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5103,19 +5103,19 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.497585174374251</v>
+        <v>-0.5026677827599713</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.4960094785615468</v>
+        <v>-0.5010998204702162</v>
       </c>
       <c r="I41" t="n">
         <v>-7</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.04460137099650296</v>
+        <v>-0.005715350044411593</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.04462482826166081</v>
+        <v>-0.005715770953983679</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5147,19 +5147,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.1479391189364208</v>
+        <v>-0.1495282548514183</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.147799527967635</v>
+        <v>-0.1493891918198074</v>
       </c>
       <c r="I42" t="n">
         <v>-7</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.05049960184971525</v>
+        <v>-0.0006354032212527727</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.0505296616636457</v>
+        <v>-0.0006354084257651493</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5191,22 +5191,22 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1479396705116471</v>
+        <v>0.149528813980055</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1480795196451083</v>
+        <v>0.1496681445836998</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04872833704688873</v>
+        <v>0.0007427146507410498</v>
       </c>
       <c r="K43" t="n">
-        <v>0.04870016582139414</v>
+        <v>0.0007427075390324944</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -5235,19 +5235,19 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.138041424371437</v>
+        <v>-0.1378246159048899</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1379198794041088</v>
+        <v>-0.1377064610882712</v>
       </c>
       <c r="I44" t="n">
         <v>-7</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.01476203557841416</v>
+        <v>-0.01160265948838912</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.01476461031073484</v>
+        <v>-0.01160439333632723</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.138012652972634</v>
+        <v>0.1377972185196086</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1381343560601636</v>
+        <v>0.1379155349787311</v>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0.01476365500144539</v>
+        <v>0.01161194463018944</v>
       </c>
       <c r="K45" t="n">
-        <v>0.01476107470345767</v>
+        <v>0.01161020474251728</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5323,19 +5323,19 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.09233762537775192</v>
+        <v>-0.0926763914846731</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.09228322531407684</v>
+        <v>-0.09262295202483983</v>
       </c>
       <c r="I46" t="n">
         <v>-7</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.008442783563111789</v>
+        <v>-0.006077089167092709</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.00844362610559557</v>
+        <v>-0.006077565029748655</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5367,22 +5367,22 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.09233917383684798</v>
+        <v>0.09267907367299699</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09239363824863744</v>
+        <v>0.09273257968823145</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>0.008446460204481809</v>
+        <v>0.006083536241462184</v>
       </c>
       <c r="K47" t="n">
-        <v>0.00844561599173943</v>
+        <v>0.006083058899363891</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5411,22 +5411,22 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.07412769454506929</v>
+        <v>0.07249696604404221</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07416279015282612</v>
+        <v>0.07252970184146079</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
-        <v>0.02083595572534591</v>
+        <v>0.01380129719432688</v>
       </c>
       <c r="K48" t="n">
-        <v>0.02083081432601119</v>
+        <v>0.01379883893454803</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5455,19 +5455,19 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.07404697831080398</v>
+        <v>-0.07241636124476258</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.07401199135009051</v>
+        <v>-0.07238372849258212</v>
       </c>
       <c r="I49" t="n">
         <v>-7</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.0208539691937375</v>
+        <v>-0.01382172051599895</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0208591053985856</v>
+        <v>-0.01382418055472101</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -5499,19 +5499,19 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.06466792763177409</v>
+        <v>0.06506168441524096</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06469463580410206</v>
+        <v>0.06508804853248762</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>0.004196803015524608</v>
+        <v>0.003530702563992349</v>
       </c>
       <c r="K50" t="n">
-        <v>0.004196594653514296</v>
+        <v>0.00353054181427126</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -5543,19 +5543,19 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.06466181198399568</v>
+        <v>-0.0650547974361757</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.0646351303340964</v>
+        <v>-0.06502846085021474</v>
       </c>
       <c r="I51" t="n">
         <v>-7</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.00419305607386633</v>
+        <v>-0.003525963905957497</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.004193263949368031</v>
+        <v>-0.00352612413300335</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -5587,19 +5587,19 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.0003117599163715568</v>
+        <v>0.0002944977304366603</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.0003117592958972182</v>
+        <v>0.0002944982703638743</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>0.005503970458335061</v>
+        <v>-0.001432429526609269</v>
       </c>
       <c r="K52" t="n">
-        <v>0.005503612056010354</v>
+        <v>-0.001432455975056257</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -5631,19 +5631,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0003136634045972642</v>
+        <v>-0.0002925914236868721</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0003136640326886209</v>
+        <v>-0.0002925908906945551</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.005488062810165673</v>
+        <v>0.001434067382227511</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.005488418886507418</v>
+        <v>0.001434040867117403</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -5675,19 +5675,19 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0002294176807424719</v>
+        <v>-0.0002722424062540085</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0002294180167439208</v>
+        <v>-0.0002722419447991342</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.005506348003891048</v>
+        <v>0.00175305873105458</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005506706456515076</v>
+        <v>0.001753019107042064</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -5719,19 +5719,19 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-0.0002303058985546613</v>
+        <v>0.0002713537680847367</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.0002303055599384152</v>
+        <v>0.0002713542264984881</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.005525710517765958</v>
+        <v>-0.001749002251642651</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005525349278045155</v>
+        <v>-0.001749041681321728</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -5763,22 +5763,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.07144556704380989</v>
+        <v>0.0653488337950705</v>
       </c>
       <c r="H56" t="n">
-        <v>0.07147816835944809</v>
+        <v>0.06537543119043221</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0711179667909505</v>
+        <v>0.03302167440587311</v>
       </c>
       <c r="K56" t="n">
-        <v>0.0710578730406084</v>
+        <v>0.03300757965514123</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -5807,19 +5807,19 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>-0.06987753245149975</v>
+        <v>-0.06376641874709321</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06984637385093606</v>
+        <v>-0.06374111478891109</v>
       </c>
       <c r="I57" t="n">
         <v>-7</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.07092398172898839</v>
+        <v>-0.03315668993595722</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.07098319290935962</v>
+        <v>-0.03317082432563012</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.0524134055185641</v>
+        <v>-0.0527212938225432</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.05239587338215301</v>
+        <v>-0.05270399536840387</v>
       </c>
       <c r="I58" t="n">
         <v>-7</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.005917393821441408</v>
+        <v>-0.001542233998918618</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.005917807776931738</v>
+        <v>-0.001542264657373948</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -5895,19 +5895,19 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.05241783576025227</v>
+        <v>0.05272605119714058</v>
       </c>
       <c r="H59" t="n">
-        <v>0.05243538229751721</v>
+        <v>0.05274336445839367</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>0.005918532913646857</v>
+        <v>0.001541899452703888</v>
       </c>
       <c r="K59" t="n">
-        <v>0.005918118476600398</v>
+        <v>0.001541868799904478</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5939,19 +5939,19 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.05165794595876605</v>
+        <v>0.05199114804347005</v>
       </c>
       <c r="H60" t="n">
-        <v>0.05167498736656739</v>
+        <v>0.05200798195971856</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>0.00543734055856504</v>
+        <v>0.001234434723002664</v>
       </c>
       <c r="K60" t="n">
-        <v>0.005436990782733631</v>
+        <v>0.001234415076581286</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -5983,19 +5983,19 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0516527483435425</v>
+        <v>-0.05198560380722483</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.05163572130922489</v>
+        <v>-0.05196878468180444</v>
       </c>
       <c r="I61" t="n">
         <v>-7</v>
       </c>
       <c r="J61" t="n">
-        <v>-0.005436343210284633</v>
+        <v>-0.001234682004437104</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.005436692608100202</v>
+        <v>-0.001234701654809101</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -6027,22 +6027,22 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.5771798890968967</v>
+        <v>0.5800501631628379</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5793142090425931</v>
+        <v>0.5821525459415398</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0.05863148693328668</v>
+        <v>0.03905749287173421</v>
       </c>
       <c r="K62" t="n">
-        <v>0.05859067542188967</v>
+        <v>0.03903776509743295</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6071,19 +6071,19 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.576853994480814</v>
+        <v>-0.5796795070425844</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5747373315795983</v>
+        <v>-0.5775953436948953</v>
       </c>
       <c r="I63" t="n">
         <v>-7</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.06166646542038734</v>
+        <v>-0.03887222671276191</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.06171125580205228</v>
+        <v>-0.03889164500562003</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -6115,19 +6115,19 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-0.2152979207969565</v>
+        <v>-0.2183849819409716</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2150024000457336</v>
+        <v>-0.2180884863981305</v>
       </c>
       <c r="I64" t="n">
         <v>-7</v>
       </c>
       <c r="J64" t="n">
-        <v>-0.05998598353614426</v>
+        <v>-0.03655028371748159</v>
       </c>
       <c r="K64" t="n">
-        <v>-0.06002837076268719</v>
+        <v>-0.03656745473453782</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -6159,22 +6159,22 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.2156552959379212</v>
+        <v>0.2187502516412962</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2159525943844471</v>
+        <v>0.2190485736360301</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65" t="n">
-        <v>0.05420407984586717</v>
+        <v>0.03641095418332441</v>
       </c>
       <c r="K65" t="n">
-        <v>0.05416920915990886</v>
+        <v>0.03639381297708155</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6197,28 +6197,28 @@
         <v>-0.01000000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5138334518692602</v>
+        <v>-0.5022823040014543</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.027666903738522</v>
+        <v>-1.004564608002923</v>
       </c>
       <c r="G66" t="n">
-        <v>-0.2379975612793146</v>
+        <v>-0.2387176307168204</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.733502884253284</v>
+        <v>-3.689030172990982</v>
       </c>
       <c r="I66" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J66" t="n">
-        <v>-0.04030725970707039</v>
+        <v>-0.0247550162111807</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.9118919964324945</v>
+        <v>-0.9123518213127326</v>
       </c>
       <c r="L66" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
@@ -6241,28 +6241,28 @@
         <v>0.01000000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>0.5023639551757455</v>
+        <v>0.4912479827360485</v>
       </c>
       <c r="F67" t="n">
-        <v>1.004727910351493</v>
+        <v>0.9824959654720802</v>
       </c>
       <c r="G67" t="n">
-        <v>0.2380158870038258</v>
+        <v>0.2387403644314645</v>
       </c>
       <c r="H67" t="n">
-        <v>3.842515060632337</v>
+        <v>3.790950783821103</v>
       </c>
       <c r="I67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
-        <v>0.04033032842163209</v>
+        <v>0.0247637761927777</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8723199806022208</v>
+        <v>0.8699761943961661</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -6285,28 +6285,28 @@
         <v>-0.01000000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>0.5943857262129342</v>
+        <v>0.5880141919554163</v>
       </c>
       <c r="F68" t="n">
-        <v>1.188771452425858</v>
+        <v>1.176028383910821</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2686217749013906</v>
+        <v>0.2706849689622857</v>
       </c>
       <c r="H68" t="n">
-        <v>4.56802301494622</v>
+        <v>4.560124260321686</v>
       </c>
       <c r="I68" t="n">
         <v>4</v>
       </c>
       <c r="J68" t="n">
-        <v>0.02295313019804013</v>
+        <v>0.01550497797421002</v>
       </c>
       <c r="K68" t="n">
-        <v>1.029807346815936</v>
+        <v>1.038378926575056</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -6329,28 +6329,28 @@
         <v>0.01000000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5811181876813976</v>
+        <v>-0.5750964812358319</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.162236375362792</v>
+        <v>-1.150192962471674</v>
       </c>
       <c r="G69" t="n">
-        <v>-0.2684251518186329</v>
+        <v>-0.2704749313194839</v>
       </c>
       <c r="H69" t="n">
-        <v>-4.208446175073817</v>
+        <v>-4.208977236888472</v>
       </c>
       <c r="I69" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.0229139518089454</v>
+        <v>-0.01544714907371514</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.032560307591311</v>
+        <v>-1.046214606966224</v>
       </c>
       <c r="L69" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="70">
@@ -6379,22 +6379,22 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3900978549826561</v>
+        <v>0.3923644308817416</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3910716921897972</v>
+        <v>0.3933252590304619</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70" t="n">
-        <v>-0.933007240792449</v>
+        <v>-0.9664600228725178</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.942607298621617</v>
+        <v>-0.9774879230438387</v>
       </c>
       <c r="L70" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="71">
@@ -6423,22 +6423,22 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.3898617642429087</v>
+        <v>-0.3921137703882778</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.3888938124657955</v>
+        <v>-0.3911589772790194</v>
       </c>
       <c r="I71" t="n">
         <v>-7</v>
       </c>
       <c r="J71" t="n">
-        <v>0.9331099947952737</v>
+        <v>0.9664290615746438</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9222453416502034</v>
+        <v>0.9535227110913382</v>
       </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6467,22 +6467,22 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.3898617642429087</v>
+        <v>-0.3921137703882778</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.3888938124657955</v>
+        <v>-0.3911589772790194</v>
       </c>
       <c r="I72" t="n">
         <v>-7</v>
       </c>
       <c r="J72" t="n">
-        <v>0.9331099947952737</v>
+        <v>0.9664290615746438</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9222453416502034</v>
+        <v>0.9535227110913382</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -6511,22 +6511,22 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3900978549826561</v>
+        <v>0.3923644308817416</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3910716921897972</v>
+        <v>0.3933252590304619</v>
       </c>
       <c r="I73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
-        <v>-0.933007240792449</v>
+        <v>-0.9664600228725178</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.942607298621617</v>
+        <v>-0.9774879230438387</v>
       </c>
       <c r="L73" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="74">
@@ -6555,19 +6555,19 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.7843178198200178</v>
+        <v>-0.7886009917272077</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7804100225910702</v>
+        <v>-0.7847490693985719</v>
       </c>
       <c r="I74" t="n">
         <v>-7</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0009805489318779337</v>
+        <v>-0.001281643318428394</v>
       </c>
       <c r="K74" t="n">
-        <v>0.000980537560110406</v>
+        <v>-0.001281664491955326</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -6599,19 +6599,19 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.7836558725217913</v>
+        <v>0.7879198876664759</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7875953090805012</v>
+        <v>0.7918041708803685</v>
       </c>
       <c r="I75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.0009779890631378407</v>
+        <v>0.00128710210945826</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.0009780003741539645</v>
+        <v>0.001287080750742575</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -6643,19 +6643,19 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.7836558725217913</v>
+        <v>0.7879198876664759</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7875953090805012</v>
+        <v>0.7918041708803685</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>-0.0009779890631378407</v>
+        <v>0.00128710210945826</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.0009780003741539645</v>
+        <v>0.001287080750742575</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -6687,19 +6687,19 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.7843178198200178</v>
+        <v>-0.7886009917272077</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.7804100225910702</v>
+        <v>-0.7847490693985719</v>
       </c>
       <c r="I77" t="n">
         <v>-7</v>
       </c>
       <c r="J77" t="n">
-        <v>0.0009805489318779337</v>
+        <v>-0.001281643318428394</v>
       </c>
       <c r="K77" t="n">
-        <v>0.000980537560110406</v>
+        <v>-0.001281664491955326</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -6731,22 +6731,22 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.04454303198235721</v>
+        <v>0.0333366559562478</v>
       </c>
       <c r="H78" t="n">
-        <v>0.04455570183498025</v>
+        <v>0.03334357615565864</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01398948010943712</v>
+        <v>-0.003704670406108335</v>
       </c>
       <c r="K78" t="n">
-        <v>0.01398716344443329</v>
+        <v>-0.003704847283771073</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6775,19 +6775,19 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>-0.04452354916381296</v>
+        <v>-0.03332424929882905</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.04451089740277325</v>
+        <v>-0.03331733720011698</v>
       </c>
       <c r="I79" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.01389932868244159</v>
+        <v>0.003723384593605772</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.01390161139882906</v>
+        <v>0.00372320581706731</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -6819,22 +6819,22 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.1482582552740155</v>
+        <v>0.1393363836790797</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1483987076569804</v>
+        <v>0.139457359225645</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
-        <v>0.01992470030641869</v>
+        <v>-0.00129628159260875</v>
       </c>
       <c r="K80" t="n">
-        <v>0.01991999906852016</v>
+        <v>-0.001296303252537712</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6863,19 +6863,19 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.148102509803266</v>
+        <v>-0.1391894343533977</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.1479626104654699</v>
+        <v>-0.1390689289342504</v>
       </c>
       <c r="I81" t="n">
         <v>-7</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.01984905257813097</v>
+        <v>0.001298990310900194</v>
       </c>
       <c r="K81" t="n">
-        <v>-0.01985370600920788</v>
+        <v>0.001298968555786928</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -6907,22 +6907,22 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.09684072075702943</v>
+        <v>0.08736217437726168</v>
       </c>
       <c r="H82" t="n">
-        <v>0.09690062657452359</v>
+        <v>0.08740971571143064</v>
       </c>
       <c r="I82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
-        <v>0.01056826000012023</v>
+        <v>-0.007287700162585509</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01056693818784282</v>
+        <v>-0.007288384434644968</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -6951,19 +6951,19 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.09668445739632148</v>
+        <v>-0.08721846189064308</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.09662481658293132</v>
+        <v>-0.08717112977757324</v>
       </c>
       <c r="I83" t="n">
         <v>-7</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.01049889250975866</v>
+        <v>0.007298453914167169</v>
       </c>
       <c r="K83" t="n">
-        <v>-0.0105001952224697</v>
+        <v>0.007297766811113604</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -6995,19 +6995,19 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2022045445983736</v>
+        <v>0.1971719689076679</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2024658919521869</v>
+        <v>0.1974143054311526</v>
       </c>
       <c r="I84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.02322384288500245</v>
+        <v>-0.0243780202527617</v>
       </c>
       <c r="K84" t="n">
-        <v>-0.02323021179343243</v>
+        <v>-0.02438566639010276</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -7039,22 +7039,22 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.20147803421807</v>
+        <v>-0.1964255346470338</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.2012192121593159</v>
+        <v>-0.1961856348041806</v>
       </c>
       <c r="I85" t="n">
         <v>-7</v>
       </c>
       <c r="J85" t="n">
-        <v>0.02071417990578084</v>
+        <v>0.02438069680327004</v>
       </c>
       <c r="K85" t="n">
-        <v>0.02070909846909075</v>
+        <v>0.02437301876885556</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -7083,19 +7083,19 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>-0.2593387478436568</v>
+        <v>-0.285142210747523</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.2589100776299063</v>
+        <v>-0.2846369580833823</v>
       </c>
       <c r="I86" t="n">
         <v>-7</v>
       </c>
       <c r="J86" t="n">
-        <v>0.08444487545494894</v>
+        <v>0.09267591874665726</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0843600767546846</v>
+        <v>0.09256437211526247</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -7127,19 +7127,19 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2647657639750776</v>
+        <v>0.1926977079651806</v>
       </c>
       <c r="H87" t="n">
-        <v>0.265214021639764</v>
+        <v>0.192929164398663</v>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
-        <v>-0.09062107921374718</v>
+        <v>-0.09268018903956232</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.09071761780472798</v>
+        <v>-0.09279008599712313</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -7171,19 +7171,19 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>-0.139270847277345</v>
+        <v>-0.1464280381949834</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.1391471286143826</v>
+        <v>-0.1462946792010484</v>
       </c>
       <c r="I88" t="n">
         <v>-7</v>
       </c>
       <c r="J88" t="n">
-        <v>0.001630047962727588</v>
+        <v>-0.01174620882770228</v>
       </c>
       <c r="K88" t="n">
-        <v>0.001630016535294487</v>
+        <v>-0.01174798582305669</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -7215,19 +7215,19 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0.1392284797450714</v>
+        <v>0.1464058176223659</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1393523375046755</v>
+        <v>0.1465393863426243</v>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
-        <v>-0.002943539754454605</v>
+        <v>0.01183774904701806</v>
       </c>
       <c r="K89" t="n">
-        <v>-0.002943642205757158</v>
+        <v>0.01183594080121964</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -7259,19 +7259,19 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>-0.2005251655680524</v>
+        <v>-0.2136870790959335</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.2002687843335025</v>
+        <v>-0.2134031941881176</v>
       </c>
       <c r="I90" t="n">
         <v>-7</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.1131923352337552</v>
+        <v>0.006868250646114404</v>
       </c>
       <c r="K90" t="n">
-        <v>-0.1133427234145472</v>
+        <v>0.006867642178704614</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -7303,22 +7303,22 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.2001866966944874</v>
+        <v>0.1915616309309769</v>
       </c>
       <c r="H91" t="n">
-        <v>0.2004428507829914</v>
+        <v>0.1917903645860974</v>
       </c>
       <c r="I91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
-        <v>0.04716134707042841</v>
+        <v>-0.01318466591529699</v>
       </c>
       <c r="K91" t="n">
-        <v>0.0471349612347467</v>
+        <v>-0.01318690452529125</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -7347,19 +7347,19 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>-0.03054756491948751</v>
+        <v>-0.02136866020504158</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.03054160881353596</v>
+        <v>-0.02136581785839553</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.002587193868507143</v>
+        <v>-0.001839179172314687</v>
       </c>
       <c r="K92" t="n">
-        <v>-0.002587273017574887</v>
+        <v>-0.001839222772410665</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -7391,19 +7391,19 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.03054502736435438</v>
+        <v>0.02136634021070449</v>
       </c>
       <c r="H93" t="n">
-        <v>0.03055098474408169</v>
+        <v>0.02136918271787636</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0.00258890866564343</v>
+        <v>0.001840204403031009</v>
       </c>
       <c r="K93" t="n">
-        <v>0.002588829384670532</v>
+        <v>0.001840160741323871</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -7435,19 +7435,19 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.0722326702310454</v>
+        <v>-0.0652975352095666</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.07219937639879959</v>
+        <v>-0.06527100175983946</v>
       </c>
       <c r="I94" t="n">
         <v>-7</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.01070004102827227</v>
+        <v>-0.004228975010974523</v>
       </c>
       <c r="K94" t="n">
-        <v>-0.0107013941186338</v>
+        <v>-0.004229205486936394</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -7479,22 +7479,22 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.07223240434504419</v>
+        <v>0.0652985418903711</v>
       </c>
       <c r="H95" t="n">
-        <v>0.07226572786078123</v>
+        <v>0.06532509835469114</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>0.0107010230983775</v>
+        <v>0.004228841439136488</v>
       </c>
       <c r="K95" t="n">
-        <v>0.01069966785534149</v>
+        <v>0.004228610820035783</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7523,19 +7523,19 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>-0.1555003437061373</v>
+        <v>-0.149366314819531</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.1553461262789426</v>
+        <v>-0.1492275526925368</v>
       </c>
       <c r="I96" t="n">
         <v>-7</v>
       </c>
       <c r="J96" t="n">
-        <v>-0.02152991300633289</v>
+        <v>-0.01612121562266111</v>
       </c>
       <c r="K96" t="n">
-        <v>-0.02153538732440552</v>
+        <v>-0.01612456167124066</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -7567,22 +7567,22 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.155471683298515</v>
+        <v>0.1493398104765333</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1556261423409637</v>
+        <v>0.1494787889092777</v>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
-        <v>0.02154170740023886</v>
+        <v>0.01614152860116036</v>
       </c>
       <c r="K97" t="n">
-        <v>0.02153621155179763</v>
+        <v>0.01613816535094514</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7611,19 +7611,19 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>-0.1782138532396971</v>
+        <v>-0.1723597387637028</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.1780113220085866</v>
+        <v>-0.1721749936237984</v>
       </c>
       <c r="I98" t="n">
         <v>-7</v>
       </c>
       <c r="J98" t="n">
-        <v>-0.0685858939337507</v>
+        <v>-0.04350274783443808</v>
       </c>
       <c r="K98" t="n">
-        <v>-0.06864127421415844</v>
+        <v>-0.04352705874980956</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -7655,19 +7655,19 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>0.178300800431515</v>
+        <v>0.1724458091669305</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1785039793640806</v>
+        <v>0.1726311475819671</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>0.06835823174107958</v>
+        <v>0.04344964521855843</v>
       </c>
       <c r="K99" t="n">
-        <v>0.06830272124818038</v>
+        <v>0.04342522246864178</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -7743,22 +7743,22 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0.5624962667984335</v>
+        <v>0.5544143877584986</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5645231907551818</v>
+        <v>0.5563347342884981</v>
       </c>
       <c r="I101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>0.04451242191710492</v>
+        <v>0.02814412479764172</v>
       </c>
       <c r="K101" t="n">
-        <v>0.04448892091979673</v>
+        <v>0.02813389034392344</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -7787,22 +7787,22 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0.193337641241925</v>
+        <v>0.1961968417956257</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1935765572818013</v>
+        <v>0.1964367857743241</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>0.04682722982371956</v>
+        <v>0.0279193870844594</v>
       </c>
       <c r="K102" t="n">
-        <v>0.04680121709108676</v>
+        <v>0.02790931560919319</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -7831,19 +7831,19 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.1933335668706775</v>
+        <v>-0.1961917367967487</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.193095234772386</v>
+        <v>-0.1959524073409398</v>
       </c>
       <c r="I103" t="n">
         <v>-7</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.04679624257281745</v>
+        <v>-0.027944464797649</v>
       </c>
       <c r="K103" t="n">
-        <v>-0.04682206157671942</v>
+        <v>-0.02795450889131246</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
@@ -7875,19 +7875,19 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>-1.406371670588982</v>
+        <v>-1.401305106478532</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.393857225986181</v>
+        <v>-1.389191651679738</v>
       </c>
       <c r="I104" t="n">
         <v>-7</v>
       </c>
       <c r="J104" t="n">
-        <v>-0.1880103195176375</v>
+        <v>-0.07583481933638581</v>
       </c>
       <c r="K104" t="n">
-        <v>-0.1884230967718636</v>
+        <v>-0.07590849991868254</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7919,22 +7919,22 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>1.406386977930907</v>
+        <v>1.245206026222604</v>
       </c>
       <c r="H105" t="n">
-        <v>1.419122569669952</v>
+        <v>1.254934881638775</v>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>0.05834701691218669</v>
+        <v>0.007566122039641243</v>
       </c>
       <c r="K105" t="n">
-        <v>0.05830660120406606</v>
+        <v>0.007565383597949449</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -7963,19 +7963,19 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.2851785542694074</v>
+        <v>-0.2857379802818514</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.2846602893212093</v>
+        <v>-0.2852306160376088</v>
       </c>
       <c r="I106" t="n">
         <v>-7</v>
       </c>
       <c r="J106" t="n">
-        <v>0.1766475202393991</v>
+        <v>0.164819756778634</v>
       </c>
       <c r="K106" t="n">
-        <v>0.1762742765396084</v>
+        <v>0.1644649460812531</v>
       </c>
       <c r="L106" t="n">
         <v>1</v>
@@ -8007,19 +8007,19 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.2849025584724814</v>
+        <v>0.2854824483683274</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2854216580869604</v>
+        <v>0.2859907612588017</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>-0.195716897305644</v>
+        <v>-0.1719439336925461</v>
       </c>
       <c r="K107" t="n">
-        <v>-0.19616396877651</v>
+        <v>-0.1723196939533054</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -8051,19 +8051,19 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.2849025584724814</v>
+        <v>0.2854824483683274</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2854216580869604</v>
+        <v>0.2859907612588017</v>
       </c>
       <c r="I108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.195716897305644</v>
+        <v>-0.1719439336925461</v>
       </c>
       <c r="K108" t="n">
-        <v>-0.19616396877651</v>
+        <v>-0.1723196939533054</v>
       </c>
       <c r="L108" t="n">
         <v>0</v>
@@ -8095,19 +8095,19 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>-0.2851785542694074</v>
+        <v>-0.2857379802818514</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.2846602893212093</v>
+        <v>-0.2852306160376088</v>
       </c>
       <c r="I109" t="n">
         <v>-7</v>
       </c>
       <c r="J109" t="n">
-        <v>0.1766475202393991</v>
+        <v>0.164819756778634</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1762742765396084</v>
+        <v>0.1644649460812531</v>
       </c>
       <c r="L109" t="n">
         <v>1</v>
@@ -8183,19 +8183,19 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>-0.7839488242118193</v>
+        <v>-0.7900490476847892</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.7800446939222354</v>
+        <v>-0.7861830030080341</v>
       </c>
       <c r="I111" t="n">
         <v>-7</v>
       </c>
       <c r="J111" t="n">
-        <v>-0.0919491266333381</v>
+        <v>-0.04797461383225965</v>
       </c>
       <c r="K111" t="n">
-        <v>-0.09204850659607189</v>
+        <v>-0.04800416890847714</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -8227,22 +8227,22 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.3277666802196677</v>
+        <v>-0.3184766304791253</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.3270822461757632</v>
+        <v>-0.3178464757664585</v>
       </c>
       <c r="I112" t="n">
         <v>-7</v>
       </c>
       <c r="J112" t="n">
-        <v>-0.2599515722263206</v>
+        <v>-0.1409328952441555</v>
       </c>
       <c r="K112" t="n">
-        <v>-0.2607367200937531</v>
+        <v>-0.1411859958149222</v>
       </c>
       <c r="L112" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -8271,19 +8271,19 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.3317730039300386</v>
+        <v>0.3225152408323311</v>
       </c>
       <c r="H113" t="n">
-        <v>0.3324771544663179</v>
+        <v>0.3231641364075415</v>
       </c>
       <c r="I113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J113" t="n">
-        <v>0.1904199113953453</v>
+        <v>0.1308774067331058</v>
       </c>
       <c r="K113" t="n">
-        <v>0.1899858261807594</v>
+        <v>0.1306542768819341</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -8359,22 +8359,22 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>-0.5912011667977595</v>
+        <v>-0.5840808692468329</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.5889781076915881</v>
+        <v>-0.581964997358341</v>
       </c>
       <c r="I115" t="n">
         <v>-7</v>
       </c>
       <c r="J115" t="n">
-        <v>-0.2652417868825481</v>
+        <v>-0.1544055039611933</v>
       </c>
       <c r="K115" t="n">
-        <v>-0.2660589109221903</v>
+        <v>-0.154708965394093</v>
       </c>
       <c r="L115" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -8403,19 +8403,19 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>-0.1559377546602718</v>
+        <v>-0.1562747622152756</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.1557826688323303</v>
+        <v>-0.1561228740239642</v>
       </c>
       <c r="I116" t="n">
         <v>-7</v>
       </c>
       <c r="J116" t="n">
-        <v>0.003321536822411986</v>
+        <v>-0.01052215699068171</v>
       </c>
       <c r="K116" t="n">
-        <v>0.003321406315187403</v>
+        <v>-0.01052358306947099</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -8447,19 +8447,19 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1558700389381613</v>
+        <v>0.1562127228983456</v>
       </c>
       <c r="H117" t="n">
-        <v>0.156025290899521</v>
+        <v>0.1563647944741717</v>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.006189524218100928</v>
+        <v>0.01062852218151278</v>
       </c>
       <c r="K117" t="n">
-        <v>-0.006189977115120371</v>
+        <v>0.01062706463434893</v>
       </c>
       <c r="L117" t="n">
         <v>0</v>
@@ -8535,22 +8535,22 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>-0.7913341294923271</v>
+        <v>-0.7847582539345979</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.7873562809650423</v>
+        <v>-0.7809436837677595</v>
       </c>
       <c r="I119" t="n">
         <v>-7</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.2408268606364601</v>
+        <v>-0.1455819668778204</v>
       </c>
       <c r="K119" t="n">
-        <v>-0.2415016399227952</v>
+        <v>-0.1458519362441777</v>
       </c>
       <c r="L119" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -8579,19 +8579,19 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.246467094127155</v>
+        <v>0.2430058922725209</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2468554884884782</v>
+        <v>0.2433740964711149</v>
       </c>
       <c r="I120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>0.09536727970210279</v>
+        <v>0.06017823150092028</v>
       </c>
       <c r="K120" t="n">
-        <v>0.09525905032114679</v>
+        <v>0.06013131980485298</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -8623,19 +8623,19 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>-0.2460058201272943</v>
+        <v>-0.2425464764713183</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.2456200615918931</v>
+        <v>-0.2421808017685123</v>
       </c>
       <c r="I121" t="n">
         <v>-7</v>
       </c>
       <c r="J121" t="n">
-        <v>-0.0952495803251594</v>
+        <v>-0.06029479628729462</v>
       </c>
       <c r="K121" t="n">
-        <v>-0.09535619894553093</v>
+        <v>-0.0603414332561627</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -8711,19 +8711,19 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.8013576728160103</v>
+        <v>-0.7986215802305878</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.7972786746167628</v>
+        <v>-0.7946714043515328</v>
       </c>
       <c r="I123" t="n">
         <v>-7</v>
       </c>
       <c r="J123" t="n">
-        <v>-0.1901154833916365</v>
+        <v>-0.1106601486463887</v>
       </c>
       <c r="K123" t="n">
-        <v>-0.1905374946285079</v>
+        <v>-0.1108165883788885</v>
       </c>
       <c r="L123" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -8755,19 +8755,19 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>-1.556995619542704</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>-1.542056498482197</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>0.003517584012421082</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>0.003517424455203866</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8799,22 +8799,22 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>1.573585395044375</v>
+        <v>1.201940982591907</v>
       </c>
       <c r="H125" t="n">
-        <v>1.589544968729541</v>
+        <v>1.211003101216988</v>
       </c>
       <c r="I125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>0.02719556725983807</v>
+        <v>-0.02141442631223356</v>
       </c>
       <c r="K125" t="n">
-        <v>0.02718680470064072</v>
+        <v>-0.02142032781736702</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -8843,19 +8843,19 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.824655173399691</v>
+        <v>0.521976697099177</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8290186850479699</v>
+        <v>0.5236785582254697</v>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>-0.01805826762800677</v>
+        <v>-0.037750647463902</v>
       </c>
       <c r="K126" t="n">
-        <v>-0.01806211972545668</v>
+        <v>-0.03776896304830046</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8887,22 +8887,22 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.8052543050114025</v>
+        <v>-0.9222460358472517</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.8011356440669033</v>
+        <v>-0.9169825285929676</v>
       </c>
       <c r="I127" t="n">
         <v>-7</v>
       </c>
       <c r="J127" t="n">
-        <v>0.01755534618856558</v>
+        <v>0.03743859928098914</v>
       </c>
       <c r="K127" t="n">
-        <v>0.0175516971354952</v>
+        <v>0.03742047535769188</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -8931,19 +8931,19 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>-0.4038124585850653</v>
+        <v>-0.2920466286727788</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.4027740847830898</v>
+        <v>-0.2915166350849745</v>
       </c>
       <c r="I128" t="n">
         <v>-7</v>
       </c>
       <c r="J128" t="n">
-        <v>-0.08828212710485417</v>
+        <v>-0.0710190631829235</v>
       </c>
       <c r="K128" t="n">
-        <v>-0.08837376107841521</v>
+        <v>-0.07108370860910185</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8975,19 +8975,19 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.4038742371213573</v>
+        <v>0.2920363687976817</v>
       </c>
       <c r="H129" t="n">
-        <v>0.404918159729192</v>
+        <v>0.2925683107495729</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J129" t="n">
-        <v>0.08762572080844677</v>
+        <v>0.07112411129678264</v>
       </c>
       <c r="K129" t="n">
-        <v>0.08753439482209302</v>
+        <v>0.07105852481180364</v>
       </c>
       <c r="L129" t="n">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -9019,22 +9019,22 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4687446435212337</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0.4701514084637211</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0.02145784714311816</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>0.02145239403110111</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -9063,19 +9063,19 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>-0.4668059458027471</v>
+        <v>-0.5439541773363601</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.4654188877507295</v>
+        <v>-0.5421185626586862</v>
       </c>
       <c r="I131" t="n">
         <v>-7</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.02104164786466356</v>
+        <v>-0.02739979377476942</v>
       </c>
       <c r="K131" t="n">
-        <v>-0.02104687686885853</v>
+        <v>-0.02740945056971356</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -9107,19 +9107,19 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>-0.5201096062941986</v>
+        <v>-0.4244311740522448</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.5183882709724514</v>
+        <v>-0.4233127444247771</v>
       </c>
       <c r="I132" t="n">
         <v>-7</v>
       </c>
       <c r="J132" t="n">
-        <v>-0.1700255846568623</v>
+        <v>-0.1314187626863728</v>
       </c>
       <c r="K132" t="n">
-        <v>-0.1703635876792973</v>
+        <v>-0.131639019066931</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -9151,19 +9151,19 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.5201756624126403</v>
+        <v>0.4244360916261201</v>
       </c>
       <c r="H133" t="n">
-        <v>0.5219086114549327</v>
+        <v>0.4255606426127656</v>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
-        <v>0.1571685785478536</v>
+        <v>0.1254088331664605</v>
       </c>
       <c r="K133" t="n">
-        <v>0.1568734719462768</v>
+        <v>0.1252040480394356</v>
       </c>
       <c r="L133" t="n">
         <v>1</v>
@@ -9195,19 +9195,19 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.1248036353714497</v>
+        <v>0.4107555102897038</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1249031490367543</v>
+        <v>0.4118086446260349</v>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J134" t="n">
-        <v>0.09078992907033268</v>
+        <v>0.07984682078185301</v>
       </c>
       <c r="K134" t="n">
-        <v>0.09069186847112576</v>
+        <v>0.07976410341632345</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
@@ -9239,19 +9239,19 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>-0.1240164938852786</v>
+        <v>-0.4107473011205229</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.1239183834843232</v>
+        <v>-0.4096997334632988</v>
       </c>
       <c r="I135" t="n">
         <v>-7</v>
       </c>
       <c r="J135" t="n">
-        <v>-0.09352943702840832</v>
+        <v>-0.07982163372909667</v>
       </c>
       <c r="K135" t="n">
-        <v>-0.09363225143299303</v>
+        <v>-0.0799032382576641</v>
       </c>
       <c r="L135" t="n">
         <v>0</v>
@@ -9327,19 +9327,19 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.1643388987997412</v>
+        <v>0.0727281961729318</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1645114886758563</v>
+        <v>0.07276114117465227</v>
       </c>
       <c r="I137" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J137" t="n">
-        <v>-0.01028687860740973</v>
+        <v>-0.003469350284710515</v>
       </c>
       <c r="K137" t="n">
-        <v>-0.01028812925505207</v>
+        <v>-0.003469505408496332</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.5903</v>
+        <v>-0.5986</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
@@ -9445,22 +9445,22 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-15.53243686653033</v>
+        <v>-16.04442938652178</v>
       </c>
       <c r="H2" t="n">
-        <v>-14.1666858788067</v>
+        <v>-14.634949104263</v>
       </c>
       <c r="I2" t="n">
-        <v>-15</v>
+        <v>-17</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.048667181127207</v>
+        <v>-4.226144948375712</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.169002085273668</v>
+        <v>-4.354057305972994</v>
       </c>
       <c r="L2" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="3">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4097</v>
+        <v>0.4014</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
@@ -9487,22 +9487,22 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-5.661372767243307</v>
+        <v>-8.126120881705049</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.464443000436773</v>
+        <v>-7.738382410632937</v>
       </c>
       <c r="I3" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="J3" t="n">
-        <v>1.643519287363361</v>
+        <v>1.53389388495048</v>
       </c>
       <c r="K3" t="n">
-        <v>1.608739167634447</v>
+        <v>1.500281349746892</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -9517,7 +9517,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.3817</v>
+        <v>-0.3779</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
@@ -9529,19 +9529,19 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.172298530469078</v>
+        <v>-7.390329902999326</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.007339064194952</v>
+        <v>-7.067751243891763</v>
       </c>
       <c r="I4" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6925371318494271</v>
+        <v>0.6047400707235653</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6866263322354484</v>
+        <v>0.5998063818635941</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.6183000000000001</v>
+        <v>0.6221</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -9571,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-25.25097580150029</v>
+        <v>-26.24558139227108</v>
       </c>
       <c r="H5" t="n">
-        <v>-21.98814796104662</v>
+        <v>-22.86808463167438</v>
       </c>
       <c r="I5" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="J5" t="n">
-        <v>-5.39993219412775</v>
+        <v>-5.575442164300419</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.555022353623734</v>
+        <v>-5.728214909150871</v>
       </c>
       <c r="L5" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="6">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.613</v>
+        <v>-0.6183333333</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -9613,19 +9613,19 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3.280443899935676</v>
+        <v>3.265710203988334</v>
       </c>
       <c r="H6" t="n">
-        <v>3.350488933937243</v>
+        <v>3.333438730269364</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3545734629956669</v>
+        <v>0.497338101802093</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3530532867156637</v>
+        <v>0.4940264220918138</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -9643,7 +9643,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.387</v>
+        <v>0.3816666667</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -9655,22 +9655,22 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.372230127790232</v>
+        <v>-5.415909265881339</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.253681824557361</v>
+        <v>-5.240027347636499</v>
       </c>
       <c r="I7" t="n">
         <v>-9</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8019070860504556</v>
+        <v>-0.8802387082144278</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.8090766509394527</v>
+        <v>-0.8894664533197556</v>
       </c>
       <c r="L7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
@@ -9685,7 +9685,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.3153333333</v>
+        <v>-0.3143333333</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -9697,22 +9697,22 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.779806892755573</v>
+        <v>-2.355336984348156</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.75981291189305</v>
+        <v>-2.321334976619653</v>
       </c>
       <c r="I8" t="n">
         <v>-7</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3809312255529491</v>
+        <v>-0.4504097944771104</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3826026417479795</v>
+        <v>-0.4529263676114113</v>
       </c>
       <c r="L8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.6846666667</v>
+        <v>0.6856666667</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -9739,22 +9739,22 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>7.161817017485617</v>
+        <v>7.088073730799863</v>
       </c>
       <c r="H9" t="n">
-        <v>7.502533463689588</v>
+        <v>7.41380100078652</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>1.037395777309797</v>
+        <v>1.210090654553127</v>
       </c>
       <c r="K9" t="n">
-        <v>1.023898370482136</v>
+        <v>1.189551564187418</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -9781,22 +9781,22 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.894712101250462</v>
+        <v>-8.956213878552575</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.420446768406578</v>
+        <v>-8.488367365558815</v>
       </c>
       <c r="I10" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001380186061219035</v>
+        <v>0.1032712767584059</v>
       </c>
       <c r="K10" t="n">
-        <v>0.001380163530434686</v>
+        <v>0.1031326506257955</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -9823,22 +9823,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>15.08255551424645</v>
+        <v>13.35262428162125</v>
       </c>
       <c r="H11" t="n">
-        <v>16.64418982483701</v>
+        <v>14.54127805672834</v>
       </c>
       <c r="I11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.776375033163511</v>
+        <v>-1.993896020147773</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.808501694059331</v>
+        <v>-2.035612808063306</v>
       </c>
       <c r="L11" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="12">
@@ -9865,22 +9865,22 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.947260708288724</v>
+        <v>-1.986770124096978</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.923353790510561</v>
+        <v>-1.962515968031596</v>
       </c>
       <c r="I12" t="n">
         <v>-7</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.206366718393923</v>
+        <v>-1.087766232376538</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.222035485304787</v>
+        <v>-1.101562548388713</v>
       </c>
       <c r="L12" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="13">
@@ -9907,22 +9907,22 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.021439217121156</v>
+        <v>-0.5520309793649574</v>
       </c>
       <c r="H13" t="n">
-        <v>1.028141658918059</v>
+        <v>-0.5501405478065067</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.954759146462202</v>
+        <v>1.870846023815304</v>
       </c>
       <c r="K13" t="n">
-        <v>1.904993817654592</v>
+        <v>1.819969125550934</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -9949,19 +9949,19 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5.648728751829225</v>
+        <v>4.02552979887605</v>
       </c>
       <c r="H14" t="n">
-        <v>5.859081725787377</v>
+        <v>4.128887769693449</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6068442277432382</v>
+        <v>0.552457972090501</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6023267611846777</v>
+        <v>0.5483555272195773</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -9991,22 +9991,22 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-28.4882803296646</v>
+        <v>-28.72261159584394</v>
       </c>
       <c r="H15" t="n">
-        <v>-24.49218580822432</v>
+        <v>-24.79914263442197</v>
       </c>
       <c r="I15" t="n">
         <v>-19</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.179682687720081</v>
+        <v>-3.097905373304563</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.265805288665312</v>
+        <v>-3.183493858487459</v>
       </c>
       <c r="L15" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="16">
@@ -10033,22 +10033,22 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7044052185902103</v>
+        <v>-2.285343615626942</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7012515667447303</v>
+        <v>-2.253317089815994</v>
       </c>
       <c r="I16" t="n">
         <v>-7</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.510398537418041</v>
+        <v>-1.570740073776278</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.53426315137623</v>
+        <v>-1.598010460789659</v>
       </c>
       <c r="L16" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="17">
@@ -10075,19 +10075,19 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2.306454745797481</v>
+        <v>2.193838016276288</v>
       </c>
       <c r="H17" t="n">
-        <v>2.340889234285186</v>
+        <v>2.224211150388385</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>2.495481356138193</v>
+        <v>2.661191832720526</v>
       </c>
       <c r="K17" t="n">
-        <v>2.413011946619278</v>
+        <v>2.554673722623967</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -10117,22 +10117,22 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.044053167437397</v>
+        <v>1.427804582639681</v>
       </c>
       <c r="H18" t="n">
-        <v>3.104286814434602</v>
+        <v>1.440610306948315</v>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.657789019212878</v>
+        <v>-2.530438661419915</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.722581592336518</v>
+        <v>-2.59285242972885</v>
       </c>
       <c r="L18" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="19">
@@ -10159,22 +10159,22 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.02576429820959</v>
+        <v>-19.90309574433013</v>
       </c>
       <c r="H19" t="n">
-        <v>-17.04482733613358</v>
+        <v>-17.81697458583488</v>
       </c>
       <c r="I19" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="J19" t="n">
-        <v>2.252996009314643</v>
+        <v>2.10033060361949</v>
       </c>
       <c r="K19" t="n">
-        <v>2.186243654665908</v>
+        <v>2.035507983528973</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -10201,22 +10201,22 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.121701639974788</v>
+        <v>-3.232351453093798</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.060742434725313</v>
+        <v>-3.168702746124609</v>
       </c>
       <c r="I20" t="n">
         <v>-8</v>
       </c>
       <c r="J20" t="n">
-        <v>1.383877805273521</v>
+        <v>1.310180969685554</v>
       </c>
       <c r="K20" t="n">
-        <v>1.359478487030003</v>
+        <v>1.285962433644485</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -10243,22 +10243,22 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.437602027440988</v>
+        <v>-4.07154256881222</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.400260889141407</v>
+        <v>-3.971155679311551</v>
       </c>
       <c r="I21" t="n">
         <v>-8</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.530878149819507</v>
+        <v>-4.719852669503943</v>
       </c>
       <c r="K21" t="n">
-        <v>-4.667278005979142</v>
+        <v>-4.861425617714602</v>
       </c>
       <c r="L21" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="22">
@@ -10285,22 +10285,22 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>-11.59154367510104</v>
+        <v>-11.56785452948725</v>
       </c>
       <c r="H22" t="n">
-        <v>-10.80375023001628</v>
+        <v>-10.80440544065073</v>
       </c>
       <c r="I22" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.571309267737711</v>
+        <v>-2.523815430752514</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.632644172784737</v>
+        <v>-2.585963023918396</v>
       </c>
       <c r="L22" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="23">
@@ -10327,22 +10327,22 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>22.49578746036897</v>
+        <v>20.54418339060334</v>
       </c>
       <c r="H23" t="n">
-        <v>26.04126026516653</v>
+        <v>23.4233666170764</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J23" t="n">
-        <v>4.21466665968331</v>
+        <v>4.444679186594236</v>
       </c>
       <c r="K23" t="n">
-        <v>3.972564655632141</v>
+        <v>4.133356684428492</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -10369,19 +10369,19 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>11.57772346472061</v>
+        <v>9.928509170654223</v>
       </c>
       <c r="H24" t="n">
-        <v>12.48590586937573</v>
+        <v>10.57633914882311</v>
       </c>
       <c r="I24" t="n">
         <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6534496555330662</v>
+        <v>0.8224057208159294</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6481983202244095</v>
+        <v>0.8131459406767334</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -10411,22 +10411,22 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-26.15472267207937</v>
+        <v>-27.23520770337555</v>
       </c>
       <c r="H25" t="n">
-        <v>-22.69071745768528</v>
+        <v>-23.64163717203411</v>
       </c>
       <c r="I25" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.721455070553695</v>
+        <v>-2.080445776722229</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.751799956813691</v>
+        <v>-2.125353575759718</v>
       </c>
       <c r="L25" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="26">
@@ -10441,7 +10441,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.398</v>
+        <v>-0.4153333333</v>
       </c>
       <c r="D26" t="b">
         <v>1</v>
@@ -10453,22 +10453,22 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.818967996917934</v>
+        <v>-2.592188625010635</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.798089846855902</v>
+        <v>-2.551071426621064</v>
       </c>
       <c r="I26" t="n">
         <v>-7</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.381380953050183</v>
+        <v>-1.331075379406158</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.401593700507107</v>
+        <v>-1.351200051203314</v>
       </c>
       <c r="L26" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="27">
@@ -10483,7 +10483,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.602</v>
+        <v>0.5846666667</v>
       </c>
       <c r="D27" t="b">
         <v>1</v>
@@ -10495,19 +10495,19 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>5.224385374569295</v>
+        <v>4.969428769742876</v>
       </c>
       <c r="H27" t="n">
-        <v>5.403924538399565</v>
+        <v>5.127765467649255</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.376779982754627</v>
+        <v>2.269787259472849</v>
       </c>
       <c r="K27" t="n">
-        <v>2.302218117580615</v>
+        <v>2.193512130791198</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.5466666667</v>
       </c>
       <c r="D28" t="b">
         <v>1</v>
@@ -10537,22 +10537,22 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.17629320875335</v>
+        <v>2.081420381872931</v>
       </c>
       <c r="H28" t="n">
-        <v>2.206927714404543</v>
+        <v>2.108742075679459</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>1.247937600489088</v>
+        <v>1.165854754095179</v>
       </c>
       <c r="K28" t="n">
-        <v>1.228213976992883</v>
+        <v>1.146840066696861</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -10567,7 +10567,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.4533333333</v>
       </c>
       <c r="D29" t="b">
         <v>1</v>
@@ -10579,22 +10579,22 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-3.865466122527323</v>
+        <v>-5.219991829508047</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.772476282908457</v>
+        <v>-5.056366098571004</v>
       </c>
       <c r="I29" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.6369003594614</v>
+        <v>-2.631806856042736</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.700854537375648</v>
+        <v>-2.698315811683486</v>
       </c>
       <c r="L29" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="30">
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-0.39925</v>
+        <v>-0.3923333333</v>
       </c>
       <c r="D30" t="b">
         <v>1</v>
@@ -10621,22 +10621,22 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2.917367351650853</v>
+        <v>1.319687312750716</v>
       </c>
       <c r="H30" t="n">
-        <v>2.972652134341843</v>
+        <v>1.330619838334059</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>1.075766606073543</v>
+        <v>0.9914087835895771</v>
       </c>
       <c r="K30" t="n">
-        <v>1.061225669315796</v>
+        <v>0.9778052009110354</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.60075</v>
+        <v>0.6076666667</v>
       </c>
       <c r="D31" t="b">
         <v>1</v>
@@ -10663,22 +10663,22 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-23.09263847325164</v>
+        <v>-23.63977506400968</v>
       </c>
       <c r="H31" t="n">
-        <v>-20.29667474305367</v>
+        <v>-20.81482027186354</v>
       </c>
       <c r="I31" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="J31" t="n">
-        <v>-4.650634083447123</v>
+        <v>-4.840243081251494</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.790499318820657</v>
+        <v>-4.984452219063485</v>
       </c>
       <c r="L31" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="32">
@@ -10693,7 +10693,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.55925</v>
+        <v>-0.5673333333</v>
       </c>
       <c r="D32" t="b">
         <v>1</v>
@@ -10705,22 +10705,22 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-14.87406290183804</v>
+        <v>-15.21772540873914</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.61399049017328</v>
+        <v>-13.9396727492101</v>
       </c>
       <c r="I32" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.463261680462935</v>
+        <v>-3.61789686045379</v>
       </c>
       <c r="K32" t="n">
-        <v>-3.560964238370843</v>
+        <v>-3.724249441042488</v>
       </c>
       <c r="L32" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="33">
@@ -10735,7 +10735,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.44075</v>
+        <v>0.4326666667</v>
       </c>
       <c r="D33" t="b">
         <v>1</v>
@@ -10747,19 +10747,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>6.680751071321197</v>
+        <v>4.77835802584238</v>
       </c>
       <c r="H33" t="n">
-        <v>6.976530651751148</v>
+        <v>4.924600088476438</v>
       </c>
       <c r="I33" t="n">
         <v>5</v>
       </c>
       <c r="J33" t="n">
-        <v>2.647863530289136</v>
+        <v>2.537536416817474</v>
       </c>
       <c r="K33" t="n">
-        <v>2.554642326523307</v>
+        <v>2.441147087143364</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -10789,22 +10789,22 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.052673746681421</v>
+        <v>1.420564958697838</v>
       </c>
       <c r="H34" t="n">
-        <v>2.079907243724705</v>
+        <v>1.433240588106059</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
-        <v>0.06983362726491293</v>
+        <v>0.02163362785803002</v>
       </c>
       <c r="K34" t="n">
-        <v>0.06977568920815003</v>
+        <v>0.02162758391186514</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -10831,22 +10831,22 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>-43.40379168803489</v>
+        <v>-43.70016726158872</v>
       </c>
       <c r="H35" t="n">
-        <v>-35.91562362871406</v>
+        <v>-36.41525433466654</v>
       </c>
       <c r="I35" t="n">
         <v>-23</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.825506835900754</v>
+        <v>-3.744366683122678</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.937511681193193</v>
+        <v>-3.855518559661732</v>
       </c>
       <c r="L35" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="36">
@@ -10873,19 +10873,19 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.5029907539682767</v>
+        <v>-0.5083937852620579</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.50138069161099</v>
+        <v>-0.5067899571870669</v>
       </c>
       <c r="I36" t="n">
         <v>-7</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.1793247756126277</v>
+        <v>-0.05891685234163191</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.1797005212349845</v>
+        <v>-0.05896138707213083</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -10915,22 +10915,22 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.03180538130422406</v>
+        <v>-2.10496626144058</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.03179892465738021</v>
+        <v>-2.077762302126104</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2819704679942063</v>
+        <v>-0.4628803988981787</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.282892818625939</v>
+        <v>-0.4655352660196428</v>
       </c>
       <c r="L37" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="38">
@@ -10957,19 +10957,19 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.4142107584855239</v>
+        <v>-0.4135562097623335</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4131182907829327</v>
+        <v>-0.412494284801511</v>
       </c>
       <c r="I38" t="n">
         <v>-7</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.04428178836967334</v>
+        <v>-0.03478063987400049</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.04430491117369684</v>
+        <v>-0.03479619066008866</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10999,19 +10999,19 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>17.13435089874028</v>
+        <v>17.00204466013176</v>
       </c>
       <c r="H39" t="n">
-        <v>19.16320024701608</v>
+        <v>18.95418253970968</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7666764610900216</v>
+        <v>0.793716003387587</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7594038715019096</v>
+        <v>0.7851073253928575</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -11041,19 +11041,19 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.477238285733421</v>
+        <v>-1.482522629252884</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.46343722044287</v>
+        <v>-1.468971684960422</v>
       </c>
       <c r="I40" t="n">
         <v>-7</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.134655633749496</v>
+        <v>-0.09647053913781178</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1348681511664793</v>
+        <v>-0.09658957149647307</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -11083,19 +11083,19 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>12.5726901181699</v>
+        <v>11.49666284258683</v>
       </c>
       <c r="H41" t="n">
-        <v>13.64792037807669</v>
+        <v>12.37126026294425</v>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
-        <v>0.728184800488421</v>
+        <v>0.720931701455477</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7216374153410499</v>
+        <v>0.7138639605033887</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -11125,19 +11125,19 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.565795343455477</v>
+        <v>2.51027743909188</v>
       </c>
       <c r="H42" t="n">
-        <v>2.608472609622908</v>
+        <v>2.550119478968952</v>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3138695763743584</v>
+        <v>0.271596958237609</v>
       </c>
       <c r="K42" t="n">
-        <v>0.3126812786305138</v>
+        <v>0.2706255918532534</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -11167,22 +11167,22 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-4.818165336433793</v>
+        <v>-6.35872594168498</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.674656868898097</v>
+        <v>-6.117999683787076</v>
       </c>
       <c r="I43" t="n">
         <v>-9</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.40618412775995</v>
+        <v>-1.304442875892249</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.427079662105861</v>
+        <v>-1.323827144939159</v>
       </c>
       <c r="L43" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="44">
@@ -11209,19 +11209,19 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.916384400652987</v>
+        <v>2.478555525865715</v>
       </c>
       <c r="H44" t="n">
-        <v>2.971631627390764</v>
+        <v>2.517389678850918</v>
       </c>
       <c r="I44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>0.1385466861732922</v>
+        <v>0.1182577439218875</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1383176361369749</v>
+        <v>0.1180757497297975</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -11251,19 +11251,19 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>-2.779523304310771</v>
+        <v>-2.85805659644484</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.731083193467668</v>
+        <v>-2.808164543107154</v>
       </c>
       <c r="I45" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1172213753645153</v>
+        <v>0.04542566122448477</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1170576315136955</v>
+        <v>0.0453989623307649</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -11293,22 +11293,22 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>-0.006688889448838609</v>
+        <v>-0.2984681229394823</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.006688603833339357</v>
+        <v>-0.2979145891790438</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="J46" t="n">
-        <v>0.03173487340985304</v>
+        <v>-0.03254599414276527</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03172293801725345</v>
+        <v>-0.03255961333751145</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -11335,19 +11335,19 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2226669794114002</v>
+        <v>0.1267217221991075</v>
       </c>
       <c r="H47" t="n">
-        <v>0.2229839382254397</v>
+        <v>0.1268217764904591</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9467875094890985</v>
+        <v>-0.7988207733830137</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.9566616867954707</v>
+        <v>-0.8064817504262152</v>
       </c>
       <c r="L47" t="n">
         <v>-2</v>
@@ -11377,22 +11377,22 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01457777987019426</v>
+        <v>-0.022546233969166</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01457913666419586</v>
+        <v>-0.02254306974532483</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.5368740092016324</v>
+        <v>-0.4051255063114851</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.5401555831347054</v>
+        <v>-0.4071697637118774</v>
       </c>
       <c r="L48" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="49">
@@ -11419,22 +11419,22 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1213550157935401</v>
+        <v>-0.5291477727514575</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1214491038358574</v>
+        <v>-0.5274105613365236</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0680795006530559</v>
+        <v>-0.005862191797916694</v>
       </c>
       <c r="K49" t="n">
-        <v>0.06802444291488285</v>
+        <v>-0.005862634608519102</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -11461,19 +11461,19 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1444599106937972</v>
+        <v>0.1322806095846829</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1445932554101432</v>
+        <v>0.1323896384166403</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1243701042601373</v>
+        <v>0.0659090756095182</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1241856959667658</v>
+        <v>0.06585277787041122</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -11503,22 +11503,22 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-10.91310254306254</v>
+        <v>-13.75172919627062</v>
       </c>
       <c r="H51" t="n">
-        <v>-10.21082519785199</v>
+        <v>-12.69368177963798</v>
       </c>
       <c r="I51" t="n">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.037188813564143</v>
+        <v>-4.964783390162872</v>
       </c>
       <c r="K51" t="n">
-        <v>-5.186438926714594</v>
+        <v>-5.111389659176218</v>
       </c>
       <c r="L51" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="52">
@@ -11545,19 +11545,19 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>-1.779603238465597</v>
+        <v>-1.789888346342963</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.759613806262678</v>
+        <v>-1.770176756235884</v>
       </c>
       <c r="I52" t="n">
         <v>-7</v>
       </c>
       <c r="J52" t="n">
-        <v>-0.2005545648243867</v>
+        <v>-0.0912583323603755</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.2010238528607502</v>
+        <v>-0.09136489573648277</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -11587,19 +11587,19 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>5.546944457671913</v>
+        <v>3.93308417153446</v>
       </c>
       <c r="H53" t="n">
-        <v>5.749678314360096</v>
+        <v>4.031698040814206</v>
       </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>0.1519171609063861</v>
+        <v>0.1090151249550217</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1516415364367418</v>
+        <v>0.1088605795441993</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -11629,19 +11629,19 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>3.21283952870985</v>
+        <v>2.362687237685464</v>
       </c>
       <c r="H54" t="n">
-        <v>3.280001821922639</v>
+        <v>2.397951132692526</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0975151477482683</v>
+        <v>0.05015775248526921</v>
       </c>
       <c r="K54" t="n">
-        <v>0.09740197283283436</v>
+        <v>0.05012518897818552</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
@@ -11671,19 +11671,19 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-3.732844225406041</v>
+        <v>-3.755102987488499</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.646045851858418</v>
+        <v>-3.669519942750981</v>
       </c>
       <c r="I55" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.4050733923743834</v>
+        <v>-0.2973512152398854</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.4069600384367433</v>
+        <v>-0.298462985401045</v>
       </c>
       <c r="L55" t="n">
         <v>-1</v>
@@ -11701,34 +11701,34 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-0.4752</v>
+        <v>-0.4856</v>
       </c>
       <c r="D56" t="b">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>-52.06818961625282</v>
+        <v>-52.35678365171034</v>
       </c>
       <c r="F56" t="n">
-        <v>-104.1363792325056</v>
+        <v>-104.7135673034207</v>
       </c>
       <c r="G56" t="n">
-        <v>-11.29374809892951</v>
+        <v>-11.57055422688154</v>
       </c>
       <c r="H56" t="n">
-        <v>-239.3735788138192</v>
+        <v>-240.7845567739307</v>
       </c>
       <c r="I56" t="n">
-        <v>-230</v>
+        <v>-232</v>
       </c>
       <c r="J56" t="n">
-        <v>-1.890506005119953</v>
+        <v>-1.836622973929323</v>
       </c>
       <c r="K56" t="n">
-        <v>-15.25111095800924</v>
+        <v>-15.47003071465429</v>
       </c>
       <c r="L56" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="57">
@@ -11743,34 +11743,34 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.5247999999999999</v>
+        <v>0.5144</v>
       </c>
       <c r="D57" t="b">
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="F57" t="n">
-        <v>90.02362076749435</v>
+        <v>89.44643269657929</v>
       </c>
       <c r="G57" t="n">
-        <v>15.50934525665926</v>
+        <v>13.7202155022602</v>
       </c>
       <c r="H57" t="n">
-        <v>195.6264211861797</v>
+        <v>194.2154432260691</v>
       </c>
       <c r="I57" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J57" t="n">
-        <v>1.914833652134519</v>
+        <v>1.893183372776207</v>
       </c>
       <c r="K57" t="n">
-        <v>19.74888904199076</v>
+        <v>19.52996928534571</v>
       </c>
       <c r="L57" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
@@ -11785,34 +11785,34 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.4108</v>
+        <v>-0.4148</v>
       </c>
       <c r="D58" t="b">
         <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="F58" t="n">
-        <v>90.02362076749435</v>
+        <v>89.44643269657929</v>
       </c>
       <c r="G58" t="n">
-        <v>8.020271696993859</v>
+        <v>6.438228190001382</v>
       </c>
       <c r="H58" t="n">
-        <v>195.6264211861797</v>
+        <v>194.2154432260691</v>
       </c>
       <c r="I58" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5978869371406077</v>
+        <v>0.5824729332161951</v>
       </c>
       <c r="K58" t="n">
-        <v>19.74888904199076</v>
+        <v>19.52996928534571</v>
       </c>
       <c r="L58" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59">
@@ -11827,34 +11827,34 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.5851999999999999</v>
       </c>
       <c r="D59" t="b">
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>-52.06818961625282</v>
+        <v>-52.35678365171034</v>
       </c>
       <c r="F59" t="n">
-        <v>-104.1363792325056</v>
+        <v>-104.7135673034207</v>
       </c>
       <c r="G59" t="n">
-        <v>-25.67982620530421</v>
+        <v>-26.41907006064213</v>
       </c>
       <c r="H59" t="n">
-        <v>-239.3735788138192</v>
+        <v>-240.7845567739307</v>
       </c>
       <c r="I59" t="n">
-        <v>-230</v>
+        <v>-232</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.073089702456585</v>
+        <v>-3.071524468300417</v>
       </c>
       <c r="K59" t="n">
-        <v>-15.25111095800924</v>
+        <v>-15.47003071465429</v>
       </c>
       <c r="L59" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="60">
@@ -11881,22 +11881,22 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>18.36694978059106</v>
+        <v>16.65163839286495</v>
       </c>
       <c r="H60" t="n">
-        <v>20.70665278045018</v>
+        <v>18.52203146202419</v>
       </c>
       <c r="I60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J60" t="n">
-        <v>1.697521536605947</v>
+        <v>1.72203108881191</v>
       </c>
       <c r="K60" t="n">
-        <v>1.660341039309699</v>
+        <v>1.679246043516571</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -11923,22 +11923,22 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>-37.28337586169104</v>
+        <v>-38.02374244188189</v>
       </c>
       <c r="H61" t="n">
-        <v>-31.20354307074751</v>
+        <v>-31.98100979762563</v>
       </c>
       <c r="I61" t="n">
-        <v>-21</v>
+        <v>-20</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.411151023436553</v>
+        <v>-4.588184962363037</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.54385766115616</v>
+        <v>-4.726539764781052</v>
       </c>
       <c r="L61" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="62">
@@ -11965,22 +11965,22 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>-10.29918274722314</v>
+        <v>-10.44373543847883</v>
       </c>
       <c r="H62" t="n">
-        <v>-9.670503789757163</v>
+        <v>-9.815410196102391</v>
       </c>
       <c r="I62" t="n">
         <v>-12</v>
       </c>
       <c r="J62" t="n">
-        <v>-2.837388510017533</v>
+        <v>-2.959683285858944</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.909458621245648</v>
+        <v>-3.039605551663165</v>
       </c>
       <c r="L62" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="63">
@@ -12007,19 +12007,19 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>18.49385428269724</v>
+        <v>16.52047361559173</v>
       </c>
       <c r="H63" t="n">
-        <v>20.8668476313845</v>
+        <v>18.36072952635908</v>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J63" t="n">
-        <v>3.97210835278095</v>
+        <v>3.968744570975886</v>
       </c>
       <c r="K63" t="n">
-        <v>3.75749165593129</v>
+        <v>3.722652436188895</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -12218,22 +12218,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C2" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D2" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G2" t="n">
-        <v>219.9383726917495</v>
+        <v>223.235839468429</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -12242,34 +12242,34 @@
         <v>50</v>
       </c>
       <c r="J2" t="n">
-        <v>49.56031533614195</v>
+        <v>49.95866382933372</v>
       </c>
       <c r="K2" t="n">
-        <v>239.37357881382</v>
+        <v>240.7845567739309</v>
       </c>
       <c r="L2" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003201996429522125</v>
+        <v>0.0003159383068485067</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9999999865772464</v>
+        <v>0.9999999903295805</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R2" t="n">
-        <v>49.25111095800924</v>
+        <v>49.47003071465429</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T2" t="n">
         <v>11</v>
@@ -12290,7 +12290,7 @@
         <v>0.999</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
@@ -12317,13 +12317,13 @@
         <v>-77.664</v>
       </c>
       <c r="E3" t="n">
-        <v>-84.72037923250565</v>
+        <v>-85.29756730342071</v>
       </c>
       <c r="F3" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>198.2705972653311</v>
+        <v>201.2249307602272</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -12332,28 +12332,28 @@
         <v>47</v>
       </c>
       <c r="J3" t="n">
-        <v>47.01802949979706</v>
+        <v>47.4566775584923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.004271427055626609</v>
+        <v>0.002444538359925252</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>2.275957200481571e-14</v>
+        <v>8.992806499463768e-15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00151919221996677</v>
+        <v>0.0008424094662410342</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1105366972654851</v>
+        <v>0.1082949702883258</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R3" t="n">
         <v>34</v>
@@ -12380,31 +12380,31 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA3" t="n">
-        <v>-42.36018961625282</v>
+        <v>-42.64878365171035</v>
       </c>
       <c r="AB3" t="n">
-        <v>-84.72037923250565</v>
+        <v>-85.29756730342071</v>
       </c>
       <c r="AC3" t="n">
-        <v>-21.66777542641847</v>
+        <v>-22.01090870820175</v>
       </c>
       <c r="AD3" t="n">
-        <v>-239.3693073867644</v>
+        <v>-240.782112235571</v>
       </c>
       <c r="AE3" t="n">
-        <v>-230</v>
+        <v>-232</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2.542285836344895</v>
+        <v>-2.501986270841428</v>
       </c>
       <c r="AG3" t="n">
-        <v>-15.25111095800924</v>
+        <v>-15.47003071465429</v>
       </c>
       <c r="AH3" t="n">
-        <v>-16</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="4">
@@ -12423,13 +12423,13 @@
         <v>77.66400000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>70.60762076749437</v>
+        <v>70.03043269657931</v>
       </c>
       <c r="F4" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G4" t="n">
-        <v>232.7928054670602</v>
+        <v>234.3225117880953</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -12438,31 +12438,31 @@
         <v>52</v>
       </c>
       <c r="J4" t="n">
-        <v>51.07155341535018</v>
+        <v>51.4375944933018</v>
       </c>
       <c r="K4" t="n">
-        <v>434.9999962385115</v>
+        <v>434.9999964909729</v>
       </c>
       <c r="L4" t="n">
         <v>435</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9999992351500256</v>
+        <v>0.9999993231823747</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9999999999999966</v>
+        <v>0.9999999999999984</v>
       </c>
       <c r="O4" t="n">
-        <v>0.910536697265485</v>
+        <v>0.9082949702883258</v>
       </c>
       <c r="P4" t="n">
         <v>435</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R4" t="n">
-        <v>68.99999999945007</v>
+        <v>68.99999996553919</v>
       </c>
       <c r="S4" t="n">
         <v>69</v>
@@ -12480,37 +12480,37 @@
         <v>65</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9999999994501981</v>
+        <v>0.9999999655433565</v>
       </c>
       <c r="Y4" t="n">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA4" t="n">
-        <v>35.30381038374718</v>
+        <v>35.01521634828966</v>
       </c>
       <c r="AB4" t="n">
-        <v>70.60762076749437</v>
+        <v>70.03043269657931</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.8544327753107</v>
+        <v>11.08667231966635</v>
       </c>
       <c r="AD4" t="n">
-        <v>195.6264174246914</v>
+        <v>194.215439717042</v>
       </c>
       <c r="AE4" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.511238079208226</v>
+        <v>1.478930663968079</v>
       </c>
       <c r="AG4" t="n">
-        <v>19.74888904144083</v>
+        <v>19.5299692508849</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -12520,58 +12520,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C5" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D5" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G5" t="n">
-        <v>194.6873968902493</v>
+        <v>196.9902580761579</v>
       </c>
       <c r="H5" t="n">
-        <v>-25.25097580150029</v>
+        <v>-26.24558139227108</v>
       </c>
       <c r="I5" t="n">
+        <v>45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>44.3832216650333</v>
+      </c>
+      <c r="K5" t="n">
+        <v>217.9164721422565</v>
+      </c>
+      <c r="L5" t="n">
+        <v>213</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.476778858684359e-05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.999999678009311</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5476108299062733</v>
+      </c>
+      <c r="P5" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12.17479560915943</v>
+      </c>
+      <c r="R5" t="n">
+        <v>43.74181580550341</v>
+      </c>
+      <c r="S5" t="n">
         <v>44</v>
-      </c>
-      <c r="J5" t="n">
-        <v>44.1603831420142</v>
-      </c>
-      <c r="K5" t="n">
-        <v>217.3854308527734</v>
-      </c>
-      <c r="L5" t="n">
-        <v>212</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2.827656311021887e-05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.99999962511284</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.5468798123896386</v>
-      </c>
-      <c r="P5" t="n">
-        <v>230</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12.35998043335382</v>
-      </c>
-      <c r="R5" t="n">
-        <v>43.69608860438551</v>
-      </c>
-      <c r="S5" t="n">
-        <v>45</v>
       </c>
       <c r="T5" t="n">
         <v>11</v>
@@ -12586,13 +12586,13 @@
         <v>65</v>
       </c>
       <c r="X5" t="n">
-        <v>2.931674858791533e-05</v>
+        <v>3.179978138534434e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.9846994172946252</v>
+        <v>0.9854239368559278</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -12601,22 +12601,22 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-25.25097580150029</v>
+        <v>-26.24558139227108</v>
       </c>
       <c r="AD5" t="n">
-        <v>-21.98814796104662</v>
+        <v>-22.86808463167438</v>
       </c>
       <c r="AE5" t="n">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="AF5" t="n">
-        <v>-5.39993219412775</v>
+        <v>-5.575442164300419</v>
       </c>
       <c r="AG5" t="n">
-        <v>-5.555022353623734</v>
+        <v>-5.728214909150871</v>
       </c>
       <c r="AH5" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="6">
@@ -12626,55 +12626,55 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C6" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D6" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G6" t="n">
-        <v>214.2769999245062</v>
+        <v>215.1097185867239</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.661372767243307</v>
+        <v>-8.126120881705049</v>
       </c>
       <c r="I6" t="n">
         <v>52</v>
       </c>
       <c r="J6" t="n">
-        <v>51.20383462350532</v>
+        <v>51.4925577142842</v>
       </c>
       <c r="K6" t="n">
-        <v>233.9091358133833</v>
+        <v>233.046174363298</v>
       </c>
       <c r="L6" t="n">
         <v>221</v>
       </c>
       <c r="M6" t="n">
-        <v>0.000191663717846291</v>
+        <v>0.0001497193455752832</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9999999707706035</v>
+        <v>0.9999999701271129</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P6" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R6" t="n">
-        <v>50.85985012564369</v>
+        <v>50.97031206440118</v>
       </c>
       <c r="S6" t="n">
         <v>52</v>
@@ -12692,13 +12692,13 @@
         <v>65</v>
       </c>
       <c r="X6" t="n">
-        <v>0.002494188250379337</v>
+        <v>0.002254232461206263</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9996277995687433</v>
+        <v>0.9995815005173498</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -12707,22 +12707,22 @@
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>-5.661372767243307</v>
+        <v>-8.126120881705049</v>
       </c>
       <c r="AD6" t="n">
-        <v>-5.464443000436773</v>
+        <v>-7.738382410632937</v>
       </c>
       <c r="AE6" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.643519287363361</v>
+        <v>1.53389388495048</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.608739167634447</v>
+        <v>1.500281349746892</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -12732,55 +12732,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C7" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D7" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G7" t="n">
-        <v>227.1001897092352</v>
+        <v>230.3239131992289</v>
       </c>
       <c r="H7" t="n">
-        <v>7.161817017485617</v>
+        <v>7.088073730799863</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J7" t="n">
-        <v>50.59771111345175</v>
+        <v>51.16875448388685</v>
       </c>
       <c r="K7" t="n">
-        <v>246.8761122775096</v>
+        <v>248.1983577747174</v>
       </c>
       <c r="L7" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0005974786819832323</v>
+        <v>0.0005880033471709067</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9999999951150339</v>
+        <v>0.9999999964955052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P7" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R7" t="n">
-        <v>50.27500932849138</v>
+        <v>50.6595822788417</v>
       </c>
       <c r="S7" t="n">
         <v>52</v>
@@ -12798,13 +12798,13 @@
         <v>65</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001795903725541281</v>
+        <v>0.001907998051996262</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9994594330563038</v>
+        <v>0.9994945575903331</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -12813,22 +12813,22 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.161817017485617</v>
+        <v>7.088073730799863</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.502533463689588</v>
+        <v>7.41380100078652</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.037395777309797</v>
+        <v>1.210090654553127</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.023898370482136</v>
+        <v>1.189551564187418</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -12838,55 +12838,55 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C8" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D8" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G8" t="n">
-        <v>215.5661425639593</v>
+        <v>217.8199302025477</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.372230127790232</v>
+        <v>-5.415909265881339</v>
       </c>
       <c r="I8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" t="n">
-        <v>48.7584082500915</v>
+        <v>49.0784251211193</v>
       </c>
       <c r="K8" t="n">
-        <v>235.1198969892627</v>
+        <v>235.5445294262944</v>
       </c>
       <c r="L8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002157603371986117</v>
+        <v>0.0001928573207014561</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9999999754777635</v>
+        <v>0.9999999794054031</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P8" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R8" t="n">
-        <v>48.44203430706979</v>
+        <v>48.58056426133453</v>
       </c>
       <c r="S8" t="n">
         <v>49</v>
@@ -12904,13 +12904,13 @@
         <v>65</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0006231968888634198</v>
+        <v>0.0006109606701297232</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9984235293799776</v>
+        <v>0.998394344226467</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -12919,22 +12919,22 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.372230127790232</v>
+        <v>-5.415909265881339</v>
       </c>
       <c r="AD8" t="n">
-        <v>-4.253681824557361</v>
+        <v>-5.240027347636499</v>
       </c>
       <c r="AE8" t="n">
         <v>-9</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.8019070860504556</v>
+        <v>-0.8802387082144278</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.8090766509394527</v>
+        <v>-0.8894664533197556</v>
       </c>
       <c r="AH8" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
@@ -12944,58 +12944,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C9" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D9" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G9" t="n">
-        <v>235.6550334166253</v>
+        <v>237.0107883200259</v>
       </c>
       <c r="H9" t="n">
-        <v>15.71666072487574</v>
+        <v>13.77494885159695</v>
       </c>
       <c r="I9" t="n">
+        <v>54</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53.07426709491409</v>
+      </c>
+      <c r="K9" t="n">
+        <v>255.8265858199104</v>
+      </c>
+      <c r="L9" t="n">
+        <v>242</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.00102976501607499</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9999999986903431</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5476108299062733</v>
+      </c>
+      <c r="P9" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12.17479560915943</v>
+      </c>
+      <c r="R9" t="n">
+        <v>52.43732072789154</v>
+      </c>
+      <c r="S9" t="n">
         <v>53</v>
-      </c>
-      <c r="J9" t="n">
-        <v>52.69248014461421</v>
-      </c>
-      <c r="K9" t="n">
-        <v>256.78956821272</v>
-      </c>
-      <c r="L9" t="n">
-        <v>239</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.001212877447492156</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.9999999985947831</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.5468798123896386</v>
-      </c>
-      <c r="P9" t="n">
-        <v>230</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>12.35998043335382</v>
-      </c>
-      <c r="R9" t="n">
-        <v>52.25142109348921</v>
-      </c>
-      <c r="S9" t="n">
-        <v>52</v>
       </c>
       <c r="T9" t="n">
         <v>11</v>
@@ -13010,13 +13010,13 @@
         <v>65</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005356086567389617</v>
+        <v>0.004906041649158532</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.9998574714051686</v>
+        <v>0.9998397139314419</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -13025,19 +13025,19 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.71666072487574</v>
+        <v>13.77494885159695</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.41598939889994</v>
+        <v>15.04202904597955</v>
       </c>
       <c r="AE9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF9" t="n">
-        <v>3.132164808472254</v>
+        <v>3.115603265580368</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.000310135479971</v>
+        <v>2.967290013237253</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
@@ -13050,55 +13050,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C10" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D10" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G10" t="n">
-        <v>188.9261075887244</v>
+        <v>191.5427841244601</v>
       </c>
       <c r="H10" t="n">
-        <v>-31.0122651030251</v>
+        <v>-31.69305534396889</v>
       </c>
       <c r="I10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
-        <v>45.65793530908618</v>
+        <v>45.8851159430974</v>
       </c>
       <c r="K10" t="n">
-        <v>212.9483266551483</v>
+        <v>213.6871807016408</v>
       </c>
       <c r="L10" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="M10" t="n">
-        <v>1.54602890130584e-05</v>
+        <v>1.390487849217692e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.999999238439756</v>
+        <v>0.9999993658165374</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P10" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R10" t="n">
-        <v>45.23380602593097</v>
+        <v>45.27357467477539</v>
       </c>
       <c r="S10" t="n">
         <v>45</v>
@@ -13116,13 +13116,13 @@
         <v>65</v>
       </c>
       <c r="X10" t="n">
-        <v>8.465821577996469e-05</v>
+        <v>8.69377938799154e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9922308705345458</v>
+        <v>0.9923718111341829</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -13131,22 +13131,22 @@
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-31.0122651030251</v>
+        <v>-31.69305534396889</v>
       </c>
       <c r="AD10" t="n">
-        <v>-26.42525215867178</v>
+        <v>-27.0973760722901</v>
       </c>
       <c r="AE10" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="AF10" t="n">
-        <v>-3.90238002705577</v>
+        <v>-4.073547886236319</v>
       </c>
       <c r="AG10" t="n">
-        <v>-4.017304932078268</v>
+        <v>-4.196456039878896</v>
       </c>
       <c r="AH10" t="n">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="11">
@@ -13156,58 +13156,58 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C11" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D11" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G11" t="n">
-        <v>240.5496886188776</v>
+        <v>243.8027677374801</v>
       </c>
       <c r="H11" t="n">
-        <v>20.61131592712809</v>
+        <v>20.56692826905112</v>
       </c>
       <c r="I11" t="n">
         <v>51</v>
       </c>
       <c r="J11" t="n">
-        <v>50.36224189255675</v>
+        <v>50.91154436634739</v>
       </c>
       <c r="K11" t="n">
-        <v>262.9487040904925</v>
+        <v>264.237212036493</v>
       </c>
       <c r="L11" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001786108655223828</v>
+        <v>0.001773768855661051</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9999999993240269</v>
+        <v>0.9999999995307245</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P11" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R11" t="n">
-        <v>50.04506618404058</v>
+        <v>50.41037501016341</v>
       </c>
       <c r="S11" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="T11" t="n">
         <v>11</v>
@@ -13222,13 +13222,13 @@
         <v>65</v>
       </c>
       <c r="X11" t="n">
-        <v>0.001576487705466367</v>
+        <v>0.001668218309336278</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.9993768104008937</v>
+        <v>0.9994138881096615</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -13237,19 +13237,19 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.61131592712809</v>
+        <v>20.56692826905112</v>
       </c>
       <c r="AD11" t="n">
-        <v>23.57512527667242</v>
+        <v>23.45265526256213</v>
       </c>
       <c r="AE11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8019265564147986</v>
+        <v>0.9528805370136695</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.7939552260313363</v>
+        <v>0.9403442955091208</v>
       </c>
       <c r="AH11" t="n">
         <v>1</v>
@@ -13262,58 +13262,58 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52.06818961625282</v>
+        <v>52.35678365171034</v>
       </c>
       <c r="C12" t="n">
-        <v>45.01181038374718</v>
+        <v>44.72321634828965</v>
       </c>
       <c r="D12" t="n">
-        <v>7.05637923250565</v>
+        <v>7.633567303420702</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G12" t="n">
-        <v>213.6576076555276</v>
+        <v>216.9193024347928</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.280765036221908</v>
+        <v>-6.316537033636223</v>
       </c>
       <c r="I12" t="n">
         <v>50</v>
       </c>
       <c r="J12" t="n">
-        <v>49.42222108456914</v>
+        <v>49.78768851662465</v>
       </c>
       <c r="K12" t="n">
-        <v>233.3340878407257</v>
+        <v>234.7056389213595</v>
       </c>
       <c r="L12" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M12" t="n">
-        <v>0.000181003028748461</v>
+        <v>0.0001773760685311876</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9999999682083289</v>
+        <v>0.9999999766850866</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5468798123896386</v>
+        <v>0.5476108299062733</v>
       </c>
       <c r="P12" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R12" t="n">
-        <v>49.11279324904975</v>
+        <v>49.29868383300175</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T12" t="n">
         <v>11</v>
@@ -13328,13 +13328,13 @@
         <v>65</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0009229580131367987</v>
+        <v>0.0009101000686351779</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.99891709581201</v>
+        <v>0.9989020150053594</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -13343,19 +13343,19 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-6.280765036221908</v>
+        <v>-6.316537033636223</v>
       </c>
       <c r="AD12" t="n">
-        <v>-6.03949097309436</v>
+        <v>-6.078917852571408</v>
       </c>
       <c r="AE12" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1380942515728165</v>
+        <v>-0.170975312709075</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.1383177089594909</v>
+        <v>-0.1713468816525321</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -13523,13 +13523,13 @@
         <v>-77.664</v>
       </c>
       <c r="E2" t="n">
-        <v>-84.72037923250565</v>
+        <v>-85.29756730342071</v>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>198.2705972653311</v>
+        <v>201.2249307602272</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -13538,28 +13538,28 @@
         <v>47</v>
       </c>
       <c r="J2" t="n">
-        <v>47.01802949979706</v>
+        <v>47.4566775584923</v>
       </c>
       <c r="K2" t="n">
-        <v>0.004271427055626609</v>
+        <v>0.002444538359925252</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.275957200481571e-14</v>
+        <v>8.992806499463768e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00151919221996677</v>
+        <v>0.0008424094662410342</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1105366972654851</v>
+        <v>0.1082949702883258</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R2" t="n">
         <v>34</v>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="3">
@@ -13605,46 +13605,46 @@
         <v>-58.24800000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-65.30437923250567</v>
+        <v>-65.88156730342071</v>
       </c>
       <c r="F3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G3" t="n">
-        <v>203.1273867549947</v>
+        <v>206.2038839780937</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>47.61011182866474</v>
+        <v>48.06309849694068</v>
       </c>
       <c r="K3" t="n">
-        <v>4.447201988208003</v>
+        <v>3.800774445190354</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>2.299604950906087e-12</v>
+        <v>1.075362021651927e-12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5594960736395932</v>
+        <v>0.5139424949687793</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2105366972654851</v>
+        <v>0.2082949702883258</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R3" t="n">
-        <v>34.00000000001234</v>
+        <v>34.00000000006854</v>
       </c>
       <c r="S3" t="n">
         <v>34</v>
@@ -13665,10 +13665,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.200384815637562e-12</v>
+        <v>5.508793421427072e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="4">
@@ -13687,13 +13687,13 @@
         <v>-38.83199999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>-45.88837923250564</v>
+        <v>-46.4655673034207</v>
       </c>
       <c r="F4" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="G4" t="n">
-        <v>208.1079329366602</v>
+        <v>211.2028071503643</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -13702,31 +13702,31 @@
         <v>48</v>
       </c>
       <c r="J4" t="n">
-        <v>48.21763963452774</v>
+        <v>48.6769738659123</v>
       </c>
       <c r="K4" t="n">
-        <v>48.93609826285788</v>
+        <v>46.36030590120986</v>
       </c>
       <c r="L4" t="n">
         <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>4.31939428668926e-10</v>
+        <v>2.416989386411217e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9910445206941512</v>
+        <v>0.9894248965063919</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3105366972654851</v>
+        <v>0.3082949702883258</v>
       </c>
       <c r="P4" t="n">
         <v>33</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R4" t="n">
-        <v>34.00011474365584</v>
+        <v>34.00019624383491</v>
       </c>
       <c r="S4" t="n">
         <v>34</v>
@@ -13747,10 +13747,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.84346202051711e-05</v>
+        <v>0.0001363170253516621</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="5">
@@ -13769,46 +13769,46 @@
         <v>-19.416</v>
       </c>
       <c r="E5" t="n">
-        <v>-26.47237923250565</v>
+        <v>-27.0495673034207</v>
       </c>
       <c r="F5" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G5" t="n">
-        <v>213.1103570050389</v>
+        <v>216.2267771064427</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J5" t="n">
-        <v>48.83299613761112</v>
+        <v>49.29905765753127</v>
       </c>
       <c r="K5" t="n">
-        <v>149.8385359766156</v>
+        <v>146.6832458223741</v>
       </c>
       <c r="L5" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="M5" t="n">
-        <v>1.286804964806265e-07</v>
+        <v>8.622835284688435e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9999668737888819</v>
+        <v>0.9999641538790984</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4105366972654851</v>
+        <v>0.4082949702883258</v>
       </c>
       <c r="P5" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R5" t="n">
-        <v>34.40095961415142</v>
+        <v>34.40516195819973</v>
       </c>
       <c r="S5" t="n">
         <v>34</v>
@@ -13826,13 +13826,13 @@
         <v>65</v>
       </c>
       <c r="X5" t="n">
-        <v>7.578382366091319e-13</v>
+        <v>1.207145494674933e-12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1860395469160843</v>
+        <v>0.203913953093578</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="6">
@@ -13851,13 +13851,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-7.05637923250565</v>
+        <v>-7.633567303420702</v>
       </c>
       <c r="F6" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G6" t="n">
-        <v>218.1397468864083</v>
+        <v>221.2809201599848</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -13866,34 +13866,34 @@
         <v>50</v>
       </c>
       <c r="J6" t="n">
-        <v>49.45695627266279</v>
+        <v>49.86416595433454</v>
       </c>
       <c r="K6" t="n">
-        <v>216.8239700144605</v>
+        <v>216.2729051455449</v>
       </c>
       <c r="L6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>4.25952786953232e-05</v>
+        <v>3.375684386919264e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9999998997702394</v>
+        <v>0.9999999084346971</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5105366972654852</v>
+        <v>0.5082949702883257</v>
       </c>
       <c r="P6" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R6" t="n">
-        <v>42.89860587462434</v>
+        <v>42.46929620834526</v>
       </c>
       <c r="S6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T6" t="n">
         <v>11</v>
@@ -13908,13 +13908,13 @@
         <v>65</v>
       </c>
       <c r="X6" t="n">
-        <v>1.648793873282317e-05</v>
+        <v>1.358920643856898e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9787498190313945</v>
+        <v>0.9764032539391903</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="7">
@@ -13933,13 +13933,13 @@
         <v>19.416</v>
       </c>
       <c r="E7" t="n">
-        <v>12.35962076749435</v>
+        <v>11.7824326965793</v>
       </c>
       <c r="F7" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="G7" t="n">
-        <v>223.2012464944899</v>
+        <v>225.8869303587974</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -13948,31 +13948,31 @@
         <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>49.93584376935276</v>
+        <v>50.26602529121147</v>
       </c>
       <c r="K7" t="n">
-        <v>301.6809463233544</v>
+        <v>299.9041175515985</v>
       </c>
       <c r="L7" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008062556004415966</v>
+        <v>0.007321739761032842</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9999999995161714</v>
+        <v>0.9999999996373282</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6105366972654851</v>
+        <v>0.6082949702883256</v>
       </c>
       <c r="P7" t="n">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R7" t="n">
-        <v>58.6743176416153</v>
+        <v>58.30588642669247</v>
       </c>
       <c r="S7" t="n">
         <v>58</v>
@@ -13990,13 +13990,13 @@
         <v>65</v>
       </c>
       <c r="X7" t="n">
-        <v>0.06910065757638251</v>
+        <v>0.0481776351386749</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9999996284745568</v>
+        <v>0.999999194063848</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="8">
@@ -14015,13 +14015,13 @@
         <v>38.83199999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>31.77562076749434</v>
+        <v>31.19843269657929</v>
       </c>
       <c r="F8" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G8" t="n">
-        <v>227.3653800395871</v>
+        <v>228.9406485932294</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -14030,31 +14030,31 @@
         <v>51</v>
       </c>
       <c r="J8" t="n">
-        <v>50.30703681504538</v>
+        <v>50.64945766609645</v>
       </c>
       <c r="K8" t="n">
-        <v>411.8659068128292</v>
+        <v>410.8184878131538</v>
       </c>
       <c r="L8" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3050594264272483</v>
+        <v>0.3003351780998192</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9999999999953384</v>
+        <v>0.9999999999971318</v>
       </c>
       <c r="O8" t="n">
-        <v>0.710536697265485</v>
+        <v>0.7082949702883258</v>
       </c>
       <c r="P8" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R8" t="n">
-        <v>68.56526218712987</v>
+        <v>68.28958904277034</v>
       </c>
       <c r="S8" t="n">
         <v>69</v>
@@ -14072,13 +14072,13 @@
         <v>65</v>
       </c>
       <c r="X8" t="n">
-        <v>0.851540701973092</v>
+        <v>0.7547361725164904</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.9999999999999982</v>
+        <v>0.9999999999999862</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="9">
@@ -14097,13 +14097,13 @@
         <v>58.24800000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>51.19162076749436</v>
+        <v>50.61443269657931</v>
       </c>
       <c r="F9" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G9" t="n">
-        <v>230.0992405061606</v>
+        <v>231.651241884035</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14112,31 +14112,31 @@
         <v>51</v>
       </c>
       <c r="J9" t="n">
-        <v>50.68669983391275</v>
+        <v>51.04262162117158</v>
       </c>
       <c r="K9" t="n">
-        <v>434.7677551519655</v>
+        <v>434.7544019966205</v>
       </c>
       <c r="L9" t="n">
         <v>435</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9680554416504812</v>
+        <v>0.9685761775298323</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9999999999999084</v>
+        <v>0.999999999999953</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8105366972654852</v>
+        <v>0.8082949702883258</v>
       </c>
       <c r="P9" t="n">
         <v>435</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R9" t="n">
-        <v>68.99980984342301</v>
+        <v>68.99876747283841</v>
       </c>
       <c r="S9" t="n">
         <v>69</v>
@@ -14154,13 +14154,13 @@
         <v>65</v>
       </c>
       <c r="X9" t="n">
-        <v>0.99982058782649</v>
+        <v>0.9988238692922355</v>
       </c>
       <c r="Y9" t="n">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
     <row r="10">
@@ -14179,13 +14179,13 @@
         <v>77.66400000000002</v>
       </c>
       <c r="E10" t="n">
-        <v>70.60762076749437</v>
+        <v>70.03043269657931</v>
       </c>
       <c r="F10" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G10" t="n">
-        <v>232.7928054670602</v>
+        <v>234.3225117880953</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14194,31 +14194,31 @@
         <v>52</v>
       </c>
       <c r="J10" t="n">
-        <v>51.07155341535018</v>
+        <v>51.4375944933018</v>
       </c>
       <c r="K10" t="n">
-        <v>434.9999962385115</v>
+        <v>434.9999964909729</v>
       </c>
       <c r="L10" t="n">
         <v>435</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9999992351500256</v>
+        <v>0.9999993231823747</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9999999999999966</v>
+        <v>0.9999999999999984</v>
       </c>
       <c r="O10" t="n">
-        <v>0.910536697265485</v>
+        <v>0.9082949702883258</v>
       </c>
       <c r="P10" t="n">
         <v>435</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.35998043335382</v>
+        <v>12.17479560915943</v>
       </c>
       <c r="R10" t="n">
-        <v>68.99999999945007</v>
+        <v>68.99999996553919</v>
       </c>
       <c r="S10" t="n">
         <v>69</v>
@@ -14236,13 +14236,13 @@
         <v>65</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9999999994501981</v>
+        <v>0.9999999655433565</v>
       </c>
       <c r="Y10" t="n">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
     </row>
   </sheetData>
@@ -14301,7 +14301,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -14373,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -14421,7 +14421,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -14469,7 +14469,7 @@
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -14517,7 +14517,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -14541,7 +14541,7 @@
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -14613,7 +14613,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -14661,7 +14661,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -14685,7 +14685,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -14709,7 +14709,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -14757,7 +14757,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -14829,7 +14829,7 @@
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -14853,7 +14853,7 @@
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -14877,7 +14877,7 @@
         <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -14901,7 +14901,7 @@
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -14925,7 +14925,7 @@
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -14979,7 +14979,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.005503970458335061</v>
+        <v>0.001434067382227511</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.005525710517765958</v>
+        <v>0.00175305873105458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -15093,7 +15093,7 @@
         <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -15117,7 +15117,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -15147,7 +15147,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -15171,7 +15171,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -15285,13 +15285,13 @@
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7</v>
+        <v>0.03334357615565864</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -15357,7 +15357,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -15429,7 +15429,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -15459,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03055098474408169</v>
+        <v>0.02136918271787636</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -15501,7 +15501,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -15549,13 +15549,13 @@
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -15717,7 +15717,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -15765,7 +15765,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -15837,13 +15837,13 @@
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -15909,7 +15909,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -15987,7 +15987,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -16211,10 +16211,10 @@
         <v>58.8</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5075655815705793</v>
+        <v>0.6665393296904742</v>
       </c>
       <c r="U2" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -16312,10 +16312,10 @@
         <v>62.015</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02242311162407029</v>
+        <v>0.03638076840574711</v>
       </c>
       <c r="U3" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -16413,10 +16413,10 @@
         <v>46.75</v>
       </c>
       <c r="T4" t="n">
-        <v>82.87866047523954</v>
+        <v>81.96393559440212</v>
       </c>
       <c r="U4" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -16514,10 +16514,10 @@
         <v>43.28</v>
       </c>
       <c r="T5" t="n">
-        <v>97.51785463611751</v>
+        <v>97.06112078216191</v>
       </c>
       <c r="U5" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -16609,10 +16609,10 @@
         <v>52.5</v>
       </c>
       <c r="T6" t="n">
-        <v>23.26054926914467</v>
+        <v>24.10059326732469</v>
       </c>
       <c r="U6" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -16710,10 +16710,10 @@
         <v>60.81</v>
       </c>
       <c r="T7" t="n">
-        <v>0.07948561889991046</v>
+        <v>0.118259034034307</v>
       </c>
       <c r="U7" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -16811,10 +16811,10 @@
         <v>46.035</v>
       </c>
       <c r="T8" t="n">
-        <v>87.66179677355169</v>
+        <v>86.75897196188487</v>
       </c>
       <c r="U8" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -16912,10 +16912,10 @@
         <v>53.61</v>
       </c>
       <c r="T9" t="n">
-        <v>14.5817105994889</v>
+        <v>15.49972232834889</v>
       </c>
       <c r="U9" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -17013,10 +17013,10 @@
         <v>57.63</v>
       </c>
       <c r="T10" t="n">
-        <v>1.291178239650936</v>
+        <v>1.594562985858683</v>
       </c>
       <c r="U10" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -17114,10 +17114,10 @@
         <v>57.41</v>
       </c>
       <c r="T11" t="n">
-        <v>1.520958563733354</v>
+        <v>1.858459924225597</v>
       </c>
       <c r="U11" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -17215,10 +17215,10 @@
         <v>38.425</v>
       </c>
       <c r="T12" t="n">
-        <v>99.96392255535447</v>
+        <v>99.94334693101604</v>
       </c>
       <c r="U12" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -17316,10 +17316,10 @@
         <v>49.88</v>
       </c>
       <c r="T13" t="n">
-        <v>51.39816885312939</v>
+        <v>51.34607017113739</v>
       </c>
       <c r="U13" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -17417,10 +17417,10 @@
         <v>54.805</v>
       </c>
       <c r="T14" t="n">
-        <v>8.02154929202905</v>
+        <v>8.829946041156877</v>
       </c>
       <c r="U14" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -17518,10 +17518,10 @@
         <v>45.38500000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>91.11903049343699</v>
+        <v>90.28336501792842</v>
       </c>
       <c r="U15" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -17619,10 +17619,10 @@
         <v>48.13500000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>70.70540222774801</v>
+        <v>70.00312986903232</v>
       </c>
       <c r="U16" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -17714,10 +17714,10 @@
         <v>58.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6514111589839278</v>
+        <v>0.841411239704748</v>
       </c>
       <c r="U17" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -17815,10 +17815,10 @@
         <v>44.545</v>
       </c>
       <c r="T18" t="n">
-        <v>94.44759386012926</v>
+        <v>93.74974310056419</v>
       </c>
       <c r="U18" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -17916,10 +17916,10 @@
         <v>39.76</v>
       </c>
       <c r="T19" t="n">
-        <v>99.86109510896705</v>
+        <v>99.80102137541392</v>
       </c>
       <c r="U19" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -18011,10 +18011,10 @@
         <v>54</v>
       </c>
       <c r="T20" t="n">
-        <v>12.13087949165191</v>
+        <v>13.03130209045587</v>
       </c>
       <c r="U20" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -18112,10 +18112,10 @@
         <v>61.62</v>
       </c>
       <c r="T21" t="n">
-        <v>0.03438922734512184</v>
+        <v>0.05417981194230093</v>
       </c>
       <c r="U21" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -18213,10 +18213,10 @@
         <v>59.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2521095692846864</v>
+        <v>0.3469158526898442</v>
       </c>
       <c r="U22" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -18314,10 +18314,10 @@
         <v>46.255</v>
       </c>
       <c r="T23" t="n">
-        <v>86.30179517627398</v>
+        <v>85.38752136237791</v>
       </c>
       <c r="U23" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -18415,10 +18415,10 @@
         <v>65.39</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0003467317955863081</v>
+        <v>0.0007520007827055419</v>
       </c>
       <c r="U24" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -18516,10 +18516,10 @@
         <v>67.175</v>
       </c>
       <c r="T25" t="n">
-        <v>2.622668664464811e-05</v>
+        <v>6.823437890268735e-05</v>
       </c>
       <c r="U25" t="n">
-        <v>6.84656521100676</v>
+        <v>7.111663156011353</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>

--- a/outputs/Model_Sensitivity_Audit_v27.xlsx
+++ b/outputs/Model_Sensitivity_Audit_v27.xlsx
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.105200000000004</v>
+        <v>6.105200000000005</v>
       </c>
       <c r="C8" t="n">
         <v>6.287706569606078</v>
@@ -3400,7 +3400,7 @@
         <v>-0.3164969250962884</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.3158745723692391</v>
+        <v>-0.3158817462447416</v>
       </c>
       <c r="I2" t="n">
         <v>-7</v>
@@ -3442,7 +3442,7 @@
         <v>-0.8062519231254157</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8022261050652446</v>
+        <v>-0.8022723896055481</v>
       </c>
       <c r="I3" t="n">
         <v>-7</v>
@@ -3484,7 +3484,7 @@
         <v>-0.8062519231254157</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8022261050652446</v>
+        <v>-0.8022723896055481</v>
       </c>
       <c r="I4" t="n">
         <v>-7</v>
@@ -3526,7 +3526,7 @@
         <v>-0.7809055207092968</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7771282181151662</v>
+        <v>-0.7771716514060074</v>
       </c>
       <c r="I5" t="n">
         <v>-7</v>
@@ -3570,7 +3570,7 @@
         <v>-0.2998877054193656</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2993288987964888</v>
+        <v>-0.2993353407414929</v>
       </c>
       <c r="I6" t="n">
         <v>-7</v>
@@ -3614,7 +3614,7 @@
         <v>0.3010071094158207</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3015722657384572</v>
+        <v>0.301565729993257</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -3658,7 +3658,7 @@
         <v>0.2942565267130703</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2947965950182549</v>
+        <v>0.2947903496228719</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -3702,7 +3702,7 @@
         <v>-0.4512354555604077</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4499715197302123</v>
+        <v>-0.449986078727278</v>
       </c>
       <c r="I9" t="n">
         <v>-7</v>
@@ -3746,7 +3746,7 @@
         <v>0.05295180917835296</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05296927104313909</v>
+        <v>0.05296906936726486</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -3790,7 +3790,7 @@
         <v>-0.05295632009580231</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.05293886709461049</v>
+        <v>-0.05293906855604291</v>
       </c>
       <c r="I11" t="n">
         <v>-7</v>
@@ -3834,7 +3834,7 @@
         <v>-0.05558641237902862</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.05556718303432717</v>
+        <v>-0.055567404997106</v>
       </c>
       <c r="I12" t="n">
         <v>-7</v>
@@ -3878,7 +3878,7 @@
         <v>0.05559201482324738</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05561126174026754</v>
+        <v>0.0556110394448126</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -3922,7 +3922,7 @@
         <v>-0.3236011072892779</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3229505318565771</v>
+        <v>-0.3229580307734921</v>
       </c>
       <c r="I14" t="n">
         <v>-7</v>
@@ -3966,7 +3966,7 @@
         <v>0.3239052418136055</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3245597485301914</v>
+        <v>0.3245521785906647</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -4010,7 +4010,7 @@
         <v>-0.06073184963096878</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06070889629160092</v>
+        <v>-0.0607091612329782</v>
       </c>
       <c r="I16" t="n">
         <v>-7</v>
@@ -4054,7 +4054,7 @@
         <v>0.06076484571792662</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06078784188747477</v>
+        <v>0.0607875762822232</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
@@ -4098,7 +4098,7 @@
         <v>0.3032831367893039</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3038568804258261</v>
+        <v>0.3038502452940293</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
@@ -4142,7 +4142,7 @@
         <v>-0.3028200617395953</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.302250284258065</v>
+        <v>-0.302256852573521</v>
       </c>
       <c r="I19" t="n">
         <v>-7</v>
@@ -4186,7 +4186,7 @@
         <v>0.03248639367402006</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03249296533556389</v>
+        <v>0.03249288944428486</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -4230,7 +4230,7 @@
         <v>0.02949494713334389</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02950036413685098</v>
+        <v>0.02950030158083905</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>0.3143886150797925</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3150051895931938</v>
+        <v>0.3149980587259051</v>
       </c>
       <c r="I22" t="n">
         <v>2</v>
@@ -4318,7 +4318,7 @@
         <v>-0.3464141152232969</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3456686888700915</v>
+        <v>-0.3456772800551278</v>
       </c>
       <c r="I23" t="n">
         <v>-7</v>
@@ -4362,7 +4362,7 @@
         <v>-0.08090782947624575</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.08086709728820551</v>
+        <v>-0.08086756739396606</v>
       </c>
       <c r="I24" t="n">
         <v>-7</v>
@@ -4406,7 +4406,7 @@
         <v>0.2400240661790747</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2403832828423731</v>
+        <v>0.2403791300049818</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
@@ -4450,7 +4450,7 @@
         <v>-0.2351818581689713</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2348380365043852</v>
+        <v>-0.2348420014522219</v>
       </c>
       <c r="I26" t="n">
         <v>-7</v>
@@ -4494,7 +4494,7 @@
         <v>0.2351455795906077</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2354903318070569</v>
+        <v>0.2354863462919923</v>
       </c>
       <c r="I27" t="n">
         <v>2</v>
@@ -4538,7 +4538,7 @@
         <v>0.3606022311215611</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3614136329102848</v>
+        <v>0.3614042465508192</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -4582,7 +4582,7 @@
         <v>-0.3603500399918005</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3595435043455666</v>
+        <v>-0.3595527991397489</v>
       </c>
       <c r="I29" t="n">
         <v>-7</v>
@@ -4626,7 +4626,7 @@
         <v>-0.04562149713052577</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.04560854342520315</v>
+        <v>-0.04560869295667658</v>
       </c>
       <c r="I30" t="n">
         <v>-7</v>
@@ -4670,7 +4670,7 @@
         <v>0.04567669565201982</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04568968831500797</v>
+        <v>0.04568953826188249</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -4714,7 +4714,7 @@
         <v>0.03737157211730846</v>
       </c>
       <c r="H32" t="n">
-        <v>0.03738026909763903</v>
+        <v>0.03738016866003591</v>
       </c>
       <c r="I32" t="n">
         <v>2</v>
@@ -4758,7 +4758,7 @@
         <v>-0.0373455374044056</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0373368566910699</v>
+        <v>-0.03733695690146988</v>
       </c>
       <c r="I33" t="n">
         <v>-7</v>
@@ -4844,7 +4844,7 @@
         <v>0.1575828816650358</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1577376339638477</v>
+        <v>0.1577358456715388</v>
       </c>
       <c r="I35" t="n">
         <v>2</v>
@@ -4888,7 +4888,7 @@
         <v>-0.1573796752282135</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.1572256327419268</v>
+        <v>-0.1572274098886055</v>
       </c>
       <c r="I36" t="n">
         <v>-7</v>
@@ -4932,7 +4932,7 @@
         <v>-0.2758941196722446</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2754210812584006</v>
+        <v>-0.2754265351572371</v>
       </c>
       <c r="I37" t="n">
         <v>-7</v>
@@ -4976,7 +4976,7 @@
         <v>0.2761827395412979</v>
       </c>
       <c r="H38" t="n">
-        <v>0.2766584467408393</v>
+        <v>0.276652946140814</v>
       </c>
       <c r="I38" t="n">
         <v>2</v>
@@ -5062,7 +5062,7 @@
         <v>0.5039084136928977</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5054943131280538</v>
+        <v>0.505475953670981</v>
       </c>
       <c r="I40" t="n">
         <v>2</v>
@@ -5106,7 +5106,7 @@
         <v>-0.5026677827599713</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.5010998204702162</v>
+        <v>-0.5011178765345221</v>
       </c>
       <c r="I41" t="n">
         <v>-7</v>
@@ -5150,7 +5150,7 @@
         <v>-0.1495282548514183</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.1493891918198074</v>
+        <v>-0.1493907962189951</v>
       </c>
       <c r="I42" t="n">
         <v>-7</v>
@@ -5194,7 +5194,7 @@
         <v>0.149528813980055</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1496681445836998</v>
+        <v>0.149666534569775</v>
       </c>
       <c r="I43" t="n">
         <v>2</v>
@@ -5238,7 +5238,7 @@
         <v>-0.1378246159048899</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1377064610882712</v>
+        <v>-0.1377078243491781</v>
       </c>
       <c r="I44" t="n">
         <v>-7</v>
@@ -5282,7 +5282,7 @@
         <v>0.1377972185196086</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1379155349787311</v>
+        <v>0.1379141678745555</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -5326,7 +5326,7 @@
         <v>-0.0926763914846731</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.09262295202483983</v>
+        <v>-0.09262356875188971</v>
       </c>
       <c r="I46" t="n">
         <v>-7</v>
@@ -5370,7 +5370,7 @@
         <v>0.09267907367299699</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09273257968823145</v>
+        <v>0.09273196159148256</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -5414,7 +5414,7 @@
         <v>0.07249696604404221</v>
       </c>
       <c r="H48" t="n">
-        <v>0.07252970184146079</v>
+        <v>0.07252932372045962</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -5458,7 +5458,7 @@
         <v>-0.07241636124476258</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.07238372849258212</v>
+        <v>-0.07238410513645022</v>
       </c>
       <c r="I49" t="n">
         <v>-7</v>
@@ -5502,7 +5502,7 @@
         <v>0.06506168441524096</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06508804853248762</v>
+        <v>0.0650877440206159</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
@@ -5546,7 +5546,7 @@
         <v>-0.0650547974361757</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.06502846085021474</v>
+        <v>-0.06502876483622799</v>
       </c>
       <c r="I51" t="n">
         <v>-7</v>
@@ -5590,7 +5590,7 @@
         <v>0.0002944977304366603</v>
       </c>
       <c r="H52" t="n">
-        <v>0.0002944982703638743</v>
+        <v>0.00029449826413952</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>-0.0002925914236868721</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.0002925908906945551</v>
+        <v>-0.0002925908968336444</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
         <v>-0.0002722424062540085</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0002722419447991342</v>
+        <v>-0.0002722419501424156</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -5722,7 +5722,7 @@
         <v>0.0002713537680847367</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0002713542264984881</v>
+        <v>0.0002713542212120501</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -5766,7 +5766,7 @@
         <v>0.0653488337950705</v>
       </c>
       <c r="H56" t="n">
-        <v>0.06537543119043221</v>
+        <v>0.06537512398369927</v>
       </c>
       <c r="I56" t="n">
         <v>2</v>
@@ -5810,7 +5810,7 @@
         <v>-0.06376641874709321</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.06374111478891109</v>
+        <v>-0.06374140685790053</v>
       </c>
       <c r="I57" t="n">
         <v>-7</v>
@@ -5854,7 +5854,7 @@
         <v>-0.0527212938225432</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.05270399536840387</v>
+        <v>-0.05270419504614665</v>
       </c>
       <c r="I58" t="n">
         <v>-7</v>
@@ -5898,7 +5898,7 @@
         <v>0.05272605119714058</v>
       </c>
       <c r="H59" t="n">
-        <v>0.05274336445839367</v>
+        <v>0.05274316449902017</v>
       </c>
       <c r="I59" t="n">
         <v>2</v>
@@ -5942,7 +5942,7 @@
         <v>0.05199114804347005</v>
       </c>
       <c r="H60" t="n">
-        <v>0.05200798195971856</v>
+        <v>0.05200778753732038</v>
       </c>
       <c r="I60" t="n">
         <v>2</v>
@@ -5986,7 +5986,7 @@
         <v>-0.05198560380722483</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.05196878468180444</v>
+        <v>-0.05196897882734675</v>
       </c>
       <c r="I61" t="n">
         <v>-7</v>
@@ -6030,7 +6030,7 @@
         <v>0.5800501631628379</v>
       </c>
       <c r="H62" t="n">
-        <v>0.5821525459415398</v>
+        <v>0.5821281977313788</v>
       </c>
       <c r="I62" t="n">
         <v>2</v>
@@ -6074,7 +6074,7 @@
         <v>-0.5796795070425844</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5775953436948953</v>
+        <v>-0.5776193342775002</v>
       </c>
       <c r="I63" t="n">
         <v>-7</v>
@@ -6118,7 +6118,7 @@
         <v>-0.2183849819409716</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.2180884863981305</v>
+        <v>-0.218091905885359</v>
       </c>
       <c r="I64" t="n">
         <v>-7</v>
@@ -6162,7 +6162,7 @@
         <v>0.2187502516412962</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2190485736360301</v>
+        <v>0.2190451251736363</v>
       </c>
       <c r="I65" t="n">
         <v>2</v>
@@ -6206,7 +6206,7 @@
         <v>-0.2387176307168204</v>
       </c>
       <c r="H66" t="n">
-        <v>-3.689030172990982</v>
+        <v>-3.700784519408785</v>
       </c>
       <c r="I66" t="n">
         <v>-8</v>
@@ -6250,7 +6250,7 @@
         <v>0.2387403644314645</v>
       </c>
       <c r="H67" t="n">
-        <v>3.790950783821103</v>
+        <v>3.801455412391107</v>
       </c>
       <c r="I67" t="n">
         <v>2</v>
@@ -6294,10 +6294,10 @@
         <v>0.2706849689622857</v>
       </c>
       <c r="H68" t="n">
-        <v>4.560124260321686</v>
+        <v>4.572568154218601</v>
       </c>
       <c r="I68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J68" t="n">
         <v>0.01550497797421002</v>
@@ -6338,7 +6338,7 @@
         <v>-0.2704749313194839</v>
       </c>
       <c r="H69" t="n">
-        <v>-4.208977236888472</v>
+        <v>-4.222510010943466</v>
       </c>
       <c r="I69" t="n">
         <v>-8</v>
@@ -6382,7 +6382,7 @@
         <v>0.3923644308817416</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3933252590304619</v>
+        <v>0.3933141422600954</v>
       </c>
       <c r="I70" t="n">
         <v>2</v>
@@ -6426,7 +6426,7 @@
         <v>-0.3921137703882778</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.3911589772790194</v>
+        <v>-0.3911699787873886</v>
       </c>
       <c r="I71" t="n">
         <v>-7</v>
@@ -6470,7 +6470,7 @@
         <v>-0.3921137703882778</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.3911589772790194</v>
+        <v>-0.3911699787873886</v>
       </c>
       <c r="I72" t="n">
         <v>-7</v>
@@ -6514,7 +6514,7 @@
         <v>0.3923644308817416</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3933252590304619</v>
+        <v>0.3933141422600954</v>
       </c>
       <c r="I73" t="n">
         <v>2</v>
@@ -6558,7 +6558,7 @@
         <v>-0.7886009917272077</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.7847490693985719</v>
+        <v>-0.7847933588730314</v>
       </c>
       <c r="I74" t="n">
         <v>-7</v>
@@ -6602,7 +6602,7 @@
         <v>0.7879198876664759</v>
       </c>
       <c r="H75" t="n">
-        <v>0.7918041708803685</v>
+        <v>0.7917591378428313</v>
       </c>
       <c r="I75" t="n">
         <v>2</v>
@@ -6646,7 +6646,7 @@
         <v>0.7879198876664759</v>
       </c>
       <c r="H76" t="n">
-        <v>0.7918041708803685</v>
+        <v>0.7917591378428313</v>
       </c>
       <c r="I76" t="n">
         <v>2</v>
@@ -6690,7 +6690,7 @@
         <v>-0.7886009917272077</v>
       </c>
       <c r="H77" t="n">
-        <v>-0.7847490693985719</v>
+        <v>-0.7847933588730314</v>
       </c>
       <c r="I77" t="n">
         <v>-7</v>
@@ -6734,7 +6734,7 @@
         <v>0.0333366559562478</v>
       </c>
       <c r="H78" t="n">
-        <v>0.03334357615565864</v>
+        <v>0.03334349623901289</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>-0.03332424929882905</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.03331733720011698</v>
+        <v>-0.03331741699528834</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
@@ -6822,7 +6822,7 @@
         <v>0.1393363836790797</v>
       </c>
       <c r="H80" t="n">
-        <v>0.139457359225645</v>
+        <v>0.1394559613853517</v>
       </c>
       <c r="I80" t="n">
         <v>2</v>
@@ -6866,7 +6866,7 @@
         <v>-0.1391894343533977</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.1390689289342504</v>
+        <v>-0.1390703193062279</v>
       </c>
       <c r="I81" t="n">
         <v>-7</v>
@@ -6910,7 +6910,7 @@
         <v>0.08736217437726168</v>
       </c>
       <c r="H82" t="n">
-        <v>0.08740971571143064</v>
+        <v>0.08740916653346176</v>
       </c>
       <c r="I82" t="n">
         <v>2</v>
@@ -6954,7 +6954,7 @@
         <v>-0.08721846189064308</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.08717112977757324</v>
+        <v>-0.08717167603739995</v>
       </c>
       <c r="I83" t="n">
         <v>-7</v>
@@ -6998,7 +6998,7 @@
         <v>0.1971719689076679</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1974143054311526</v>
+        <v>0.1974115044502298</v>
       </c>
       <c r="I84" t="n">
         <v>2</v>
@@ -7042,7 +7042,7 @@
         <v>-0.1964255346470338</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.1961856348041806</v>
+        <v>-0.1961884018934938</v>
       </c>
       <c r="I85" t="n">
         <v>-7</v>
@@ -7086,7 +7086,7 @@
         <v>-0.285142210747523</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.2846369580833823</v>
+        <v>-0.2846427831112237</v>
       </c>
       <c r="I86" t="n">
         <v>-7</v>
@@ -7130,7 +7130,7 @@
         <v>0.1926977079651806</v>
       </c>
       <c r="H87" t="n">
-        <v>0.192929164398663</v>
+        <v>0.1929264892348215</v>
       </c>
       <c r="I87" t="n">
         <v>2</v>
@@ -7174,7 +7174,7 @@
         <v>-0.1464280381949834</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.1462946792010484</v>
+        <v>-0.1462962178167402</v>
       </c>
       <c r="I88" t="n">
         <v>-7</v>
@@ -7218,7 +7218,7 @@
         <v>0.1464058176223659</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1465393863426243</v>
+        <v>0.1465378429344923</v>
       </c>
       <c r="I89" t="n">
         <v>2</v>
@@ -7262,7 +7262,7 @@
         <v>-0.2136870790959335</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.2134031941881176</v>
+        <v>-0.2134064683179417</v>
       </c>
       <c r="I90" t="n">
         <v>-7</v>
@@ -7306,7 +7306,7 @@
         <v>0.1915616309309769</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1917903645860974</v>
+        <v>0.1917877209076551</v>
       </c>
       <c r="I91" t="n">
         <v>2</v>
@@ -7350,7 +7350,7 @@
         <v>-0.02136866020504158</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.02136581785839553</v>
+        <v>-0.02136585067330543</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
@@ -7394,7 +7394,7 @@
         <v>0.02136634021070449</v>
       </c>
       <c r="H93" t="n">
-        <v>0.02136918271787636</v>
+        <v>0.02136914989375782</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
@@ -7438,7 +7438,7 @@
         <v>-0.0652975352095666</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.06527100175983946</v>
+        <v>-0.06527130801771364</v>
       </c>
       <c r="I94" t="n">
         <v>-7</v>
@@ -7482,7 +7482,7 @@
         <v>0.0652985418903711</v>
       </c>
       <c r="H95" t="n">
-        <v>0.06532509835469114</v>
+        <v>0.06532479162081017</v>
       </c>
       <c r="I95" t="n">
         <v>2</v>
@@ -7526,7 +7526,7 @@
         <v>-0.149366314819531</v>
       </c>
       <c r="H96" t="n">
-        <v>-0.1492275526925368</v>
+        <v>-0.1492291536215475</v>
       </c>
       <c r="I96" t="n">
         <v>-7</v>
@@ -7570,7 +7570,7 @@
         <v>0.1493398104765333</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1494787889092777</v>
+        <v>0.1494771829664501</v>
       </c>
       <c r="I97" t="n">
         <v>2</v>
@@ -7614,7 +7614,7 @@
         <v>-0.1723597387637028</v>
       </c>
       <c r="H98" t="n">
-        <v>-0.1721749936237984</v>
+        <v>-0.1721771248101902</v>
       </c>
       <c r="I98" t="n">
         <v>-7</v>
@@ -7658,7 +7658,7 @@
         <v>0.1724458091669305</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1726311475819671</v>
+        <v>0.1726290056749917</v>
       </c>
       <c r="I99" t="n">
         <v>2</v>
@@ -7746,7 +7746,7 @@
         <v>0.5544143877584986</v>
       </c>
       <c r="H101" t="n">
-        <v>0.5563347342884981</v>
+        <v>0.5563124972318292</v>
       </c>
       <c r="I101" t="n">
         <v>2</v>
@@ -7790,7 +7790,7 @@
         <v>0.1961968417956257</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1964367857743241</v>
+        <v>0.1964340124610828</v>
       </c>
       <c r="I102" t="n">
         <v>2</v>
@@ -7834,7 +7834,7 @@
         <v>-0.1961917367967487</v>
       </c>
       <c r="H103" t="n">
-        <v>-0.1959524073409398</v>
+        <v>-0.1959551678546347</v>
       </c>
       <c r="I103" t="n">
         <v>-7</v>
@@ -7878,7 +7878,7 @@
         <v>-1.401305106478532</v>
       </c>
       <c r="H104" t="n">
-        <v>-1.389191651679738</v>
+        <v>-1.389330470721632</v>
       </c>
       <c r="I104" t="n">
         <v>-7</v>
@@ -7922,7 +7922,7 @@
         <v>1.245206026222604</v>
       </c>
       <c r="H105" t="n">
-        <v>1.254934881638775</v>
+        <v>1.254821825146422</v>
       </c>
       <c r="I105" t="n">
         <v>2</v>
@@ -7966,7 +7966,7 @@
         <v>-0.2857379802818514</v>
       </c>
       <c r="H106" t="n">
-        <v>-0.2852306160376088</v>
+        <v>-0.2852364653913355</v>
       </c>
       <c r="I106" t="n">
         <v>-7</v>
@@ -8010,7 +8010,7 @@
         <v>0.2854824483683274</v>
       </c>
       <c r="H107" t="n">
-        <v>0.2859907612588017</v>
+        <v>0.2859848833543879</v>
       </c>
       <c r="I107" t="n">
         <v>2</v>
@@ -8054,7 +8054,7 @@
         <v>0.2854824483683274</v>
       </c>
       <c r="H108" t="n">
-        <v>0.2859907612588017</v>
+        <v>0.2859848833543879</v>
       </c>
       <c r="I108" t="n">
         <v>2</v>
@@ -8098,7 +8098,7 @@
         <v>-0.2857379802818514</v>
       </c>
       <c r="H109" t="n">
-        <v>-0.2852306160376088</v>
+        <v>-0.2852364653913355</v>
       </c>
       <c r="I109" t="n">
         <v>-7</v>
@@ -8186,7 +8186,7 @@
         <v>-0.7900490476847892</v>
       </c>
       <c r="H111" t="n">
-        <v>-0.7861830030080341</v>
+        <v>-0.7862274545156822</v>
       </c>
       <c r="I111" t="n">
         <v>-7</v>
@@ -8230,7 +8230,7 @@
         <v>-0.3184766304791253</v>
       </c>
       <c r="H112" t="n">
-        <v>-0.3178464757664585</v>
+        <v>-0.3178537394994123</v>
       </c>
       <c r="I112" t="n">
         <v>-7</v>
@@ -8274,7 +8274,7 @@
         <v>0.3225152408323311</v>
       </c>
       <c r="H113" t="n">
-        <v>0.3231641364075415</v>
+        <v>0.323156631420062</v>
       </c>
       <c r="I113" t="n">
         <v>2</v>
@@ -8362,7 +8362,7 @@
         <v>-0.5840808692468329</v>
       </c>
       <c r="H115" t="n">
-        <v>-0.581964997358341</v>
+        <v>-0.581989352362001</v>
       </c>
       <c r="I115" t="n">
         <v>-7</v>
@@ -8406,7 +8406,7 @@
         <v>-0.1562747622152756</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.1561228740239642</v>
+        <v>-0.1561246263273119</v>
       </c>
       <c r="I116" t="n">
         <v>-7</v>
@@ -8450,7 +8450,7 @@
         <v>0.1562127228983456</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1563647944741717</v>
+        <v>0.1563630371724116</v>
       </c>
       <c r="I117" t="n">
         <v>2</v>
@@ -8538,7 +8538,7 @@
         <v>-0.7847582539345979</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.7809436837677595</v>
+        <v>-0.7809875446718024</v>
       </c>
       <c r="I119" t="n">
         <v>-7</v>
@@ -8582,7 +8582,7 @@
         <v>0.2430058922725209</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2433740964711149</v>
+        <v>0.2433698396643251</v>
       </c>
       <c r="I120" t="n">
         <v>2</v>
@@ -8626,7 +8626,7 @@
         <v>-0.2425464764713183</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.2421808017685123</v>
+        <v>-0.2421850185610595</v>
       </c>
       <c r="I121" t="n">
         <v>-7</v>
@@ -8714,7 +8714,7 @@
         <v>-0.7986215802305878</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.7946714043515328</v>
+        <v>-0.7947168211016447</v>
       </c>
       <c r="I123" t="n">
         <v>-7</v>
@@ -8758,7 +8758,7 @@
         <v>-1.556995619542704</v>
       </c>
       <c r="H124" t="n">
-        <v>-1.542056498482197</v>
+        <v>-1.542227553449351</v>
       </c>
       <c r="I124" t="n">
         <v>-7</v>
@@ -8802,7 +8802,7 @@
         <v>1.201940982591907</v>
       </c>
       <c r="H125" t="n">
-        <v>1.211003101216988</v>
+        <v>1.210897815806902</v>
       </c>
       <c r="I125" t="n">
         <v>2</v>
@@ -8846,7 +8846,7 @@
         <v>0.521976697099177</v>
       </c>
       <c r="H126" t="n">
-        <v>0.5236785582254697</v>
+        <v>0.5236588544734104</v>
       </c>
       <c r="I126" t="n">
         <v>2</v>
@@ -8890,7 +8890,7 @@
         <v>-0.9222460358472517</v>
       </c>
       <c r="H127" t="n">
-        <v>-0.9169825285929676</v>
+        <v>-0.9170430049767049</v>
       </c>
       <c r="I127" t="n">
         <v>-7</v>
@@ -8934,7 +8934,7 @@
         <v>-0.2920466286727788</v>
       </c>
       <c r="H128" t="n">
-        <v>-0.2915166350849745</v>
+        <v>-0.2915227451260307</v>
       </c>
       <c r="I128" t="n">
         <v>-7</v>
@@ -8978,7 +8978,7 @@
         <v>0.2920363687976817</v>
       </c>
       <c r="H129" t="n">
-        <v>0.2925683107495729</v>
+        <v>0.2925621593991536</v>
       </c>
       <c r="I129" t="n">
         <v>2</v>
@@ -9066,7 +9066,7 @@
         <v>-0.5439541773363601</v>
       </c>
       <c r="H131" t="n">
-        <v>-0.5421185626586862</v>
+        <v>-0.5421396962540257</v>
       </c>
       <c r="I131" t="n">
         <v>-7</v>
@@ -9110,7 +9110,7 @@
         <v>-0.4244311740522448</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.4233127444247771</v>
+        <v>-0.4233256292051522</v>
       </c>
       <c r="I132" t="n">
         <v>-7</v>
@@ -9154,7 +9154,7 @@
         <v>0.4244360916261201</v>
       </c>
       <c r="H133" t="n">
-        <v>0.4255606426127656</v>
+        <v>0.4255476294040079</v>
       </c>
       <c r="I133" t="n">
         <v>2</v>
@@ -9198,7 +9198,7 @@
         <v>0.4107555102897038</v>
       </c>
       <c r="H134" t="n">
-        <v>0.4118086446260349</v>
+        <v>0.411796458710171</v>
       </c>
       <c r="I134" t="n">
         <v>2</v>
@@ -9242,7 +9242,7 @@
         <v>-0.4107473011205229</v>
       </c>
       <c r="H135" t="n">
-        <v>-0.4096997334632988</v>
+        <v>-0.4097118027619899</v>
       </c>
       <c r="I135" t="n">
         <v>-7</v>
@@ -9330,7 +9330,7 @@
         <v>0.0727281961729318</v>
       </c>
       <c r="H137" t="n">
-        <v>0.07276114117465227</v>
+        <v>0.07276076063672576</v>
       </c>
       <c r="I137" t="n">
         <v>2</v>
@@ -9448,7 +9448,7 @@
         <v>-16.04442938652178</v>
       </c>
       <c r="H2" t="n">
-        <v>-14.634949104263</v>
+        <v>-14.64959465877899</v>
       </c>
       <c r="I2" t="n">
         <v>-17</v>
@@ -9490,10 +9490,10 @@
         <v>-8.126120881705049</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.738382410632937</v>
+        <v>-7.742650159065278</v>
       </c>
       <c r="I3" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="J3" t="n">
         <v>1.53389388495048</v>
@@ -9532,10 +9532,10 @@
         <v>-7.390329902999326</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.067751243891763</v>
+        <v>-7.071318791285734</v>
       </c>
       <c r="I4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="J4" t="n">
         <v>0.6047400707235653</v>
@@ -9574,7 +9574,7 @@
         <v>-26.24558139227108</v>
       </c>
       <c r="H5" t="n">
-        <v>-22.86808463167438</v>
+        <v>-22.90003728594155</v>
       </c>
       <c r="I5" t="n">
         <v>-19</v>
@@ -9616,7 +9616,7 @@
         <v>3.265710203988334</v>
       </c>
       <c r="H6" t="n">
-        <v>3.333438730269364</v>
+        <v>3.332643808395233</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -9658,10 +9658,10 @@
         <v>-5.415909265881339</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.240027347636499</v>
+        <v>-5.241996710943852</v>
       </c>
       <c r="I7" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J7" t="n">
         <v>-0.8802387082144278</v>
@@ -9700,7 +9700,7 @@
         <v>-2.355336984348156</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.321334976619653</v>
+        <v>-2.321722582698158</v>
       </c>
       <c r="I8" t="n">
         <v>-7</v>
@@ -9742,10 +9742,10 @@
         <v>7.088073730799863</v>
       </c>
       <c r="H9" t="n">
-        <v>7.41380100078652</v>
+        <v>7.409911537187952</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>1.210090654553127</v>
@@ -9784,10 +9784,10 @@
         <v>-8.956213878552575</v>
       </c>
       <c r="H10" t="n">
-        <v>-8.488367365558815</v>
+        <v>-8.493488600951395</v>
       </c>
       <c r="I10" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="J10" t="n">
         <v>0.1032712767584059</v>
@@ -9826,7 +9826,7 @@
         <v>13.35262428162125</v>
       </c>
       <c r="H11" t="n">
-        <v>14.54127805672834</v>
+        <v>14.52674012851446</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
@@ -9868,7 +9868,7 @@
         <v>-1.986770124096978</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.962515968031596</v>
+        <v>-1.962793023051859</v>
       </c>
       <c r="I12" t="n">
         <v>-7</v>
@@ -9910,7 +9910,7 @@
         <v>-0.5520309793649574</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5501405478065067</v>
+        <v>-0.5501623115754342</v>
       </c>
       <c r="I13" t="n">
         <v>-7</v>
@@ -9952,7 +9952,7 @@
         <v>4.02552979887605</v>
       </c>
       <c r="H14" t="n">
-        <v>4.128887769693449</v>
+        <v>4.127670308716944</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -9994,7 +9994,7 @@
         <v>-28.72261159584394</v>
       </c>
       <c r="H15" t="n">
-        <v>-24.79914263442197</v>
+        <v>-24.83527689783062</v>
       </c>
       <c r="I15" t="n">
         <v>-19</v>
@@ -10036,7 +10036,7 @@
         <v>-2.285343615626942</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.253317089815994</v>
+        <v>-2.253682319691904</v>
       </c>
       <c r="I16" t="n">
         <v>-7</v>
@@ -10078,7 +10078,7 @@
         <v>2.193838016276288</v>
       </c>
       <c r="H17" t="n">
-        <v>2.224211150388385</v>
+        <v>2.223856514089789</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
@@ -10120,7 +10120,7 @@
         <v>1.427804582639681</v>
       </c>
       <c r="H18" t="n">
-        <v>1.440610306948315</v>
+        <v>1.440461357522537</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
@@ -10162,7 +10162,7 @@
         <v>-19.90309574433013</v>
       </c>
       <c r="H19" t="n">
-        <v>-17.81697458583488</v>
+        <v>-17.83795574511527</v>
       </c>
       <c r="I19" t="n">
         <v>-18</v>
@@ -10204,7 +10204,7 @@
         <v>-3.232351453093798</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.168702746124609</v>
+        <v>-3.169424703864195</v>
       </c>
       <c r="I20" t="n">
         <v>-8</v>
@@ -10246,7 +10246,7 @@
         <v>-4.07154256881222</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.971155679311551</v>
+        <v>-3.972288808591173</v>
       </c>
       <c r="I21" t="n">
         <v>-8</v>
@@ -10288,10 +10288,10 @@
         <v>-11.56785452948725</v>
       </c>
       <c r="H22" t="n">
-        <v>-10.80440544065073</v>
+        <v>-10.8126125695054</v>
       </c>
       <c r="I22" t="n">
-        <v>-13</v>
+        <v>-12</v>
       </c>
       <c r="J22" t="n">
         <v>-2.523815430752514</v>
@@ -10330,10 +10330,10 @@
         <v>20.54418339060334</v>
       </c>
       <c r="H23" t="n">
-        <v>23.4233666170764</v>
+        <v>23.38739112019238</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
         <v>4.444679186594236</v>
@@ -10372,10 +10372,10 @@
         <v>9.928509170654223</v>
       </c>
       <c r="H24" t="n">
-        <v>10.57633914882311</v>
+        <v>10.56851395519226</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
         <v>0.8224057208159294</v>
@@ -10414,7 +10414,7 @@
         <v>-27.23520770337555</v>
       </c>
       <c r="H25" t="n">
-        <v>-23.64163717203411</v>
+        <v>-23.6752784728464</v>
       </c>
       <c r="I25" t="n">
         <v>-19</v>
@@ -10456,7 +10456,7 @@
         <v>-2.592188625010635</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.551071426621064</v>
+        <v>-2.551539517627987</v>
       </c>
       <c r="I26" t="n">
         <v>-7</v>
@@ -10498,10 +10498,10 @@
         <v>4.969428769742876</v>
       </c>
       <c r="H27" t="n">
-        <v>5.127765467649255</v>
+        <v>5.125892289647908</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
         <v>2.269787259472849</v>
@@ -10540,7 +10540,7 @@
         <v>2.081420381872931</v>
       </c>
       <c r="H28" t="n">
-        <v>2.108742075679459</v>
+        <v>2.108423245022522</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -10582,7 +10582,7 @@
         <v>-5.219991829508047</v>
       </c>
       <c r="H29" t="n">
-        <v>-5.056366098571004</v>
+        <v>-5.058200413514328</v>
       </c>
       <c r="I29" t="n">
         <v>-8</v>
@@ -10624,7 +10624,7 @@
         <v>1.319687312750716</v>
       </c>
       <c r="H30" t="n">
-        <v>1.330619838334059</v>
+        <v>1.330492746380941</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
@@ -10666,7 +10666,7 @@
         <v>-23.63977506400968</v>
       </c>
       <c r="H31" t="n">
-        <v>-20.81482027186354</v>
+        <v>-20.84226010290359</v>
       </c>
       <c r="I31" t="n">
         <v>-19</v>
@@ -10708,7 +10708,7 @@
         <v>-15.21772540873914</v>
       </c>
       <c r="H32" t="n">
-        <v>-13.9396727492101</v>
+        <v>-13.95304027403472</v>
       </c>
       <c r="I32" t="n">
         <v>-16</v>
@@ -10750,10 +10750,10 @@
         <v>4.77835802584238</v>
       </c>
       <c r="H33" t="n">
-        <v>4.924600088476438</v>
+        <v>4.922871497266385</v>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>2.537536416817474</v>
@@ -10792,7 +10792,7 @@
         <v>1.420564958697838</v>
       </c>
       <c r="H34" t="n">
-        <v>1.433240588106059</v>
+        <v>1.433093157258071</v>
       </c>
       <c r="I34" t="n">
         <v>2</v>
@@ -10834,7 +10834,7 @@
         <v>-43.70016726158872</v>
       </c>
       <c r="H35" t="n">
-        <v>-36.41525433466654</v>
+        <v>-36.46951469699007</v>
       </c>
       <c r="I35" t="n">
         <v>-23</v>
@@ -10876,7 +10876,7 @@
         <v>-0.5083937852620579</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5067899571870669</v>
+        <v>-0.5068084257046053</v>
       </c>
       <c r="I36" t="n">
         <v>-7</v>
@@ -10918,7 +10918,7 @@
         <v>-2.10496626144058</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.077762302126104</v>
+        <v>-2.078072848398534</v>
       </c>
       <c r="I37" t="n">
         <v>-7</v>
@@ -10960,7 +10960,7 @@
         <v>-0.4135562097623335</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.412494284801511</v>
+        <v>-0.4125065193317141</v>
       </c>
       <c r="I38" t="n">
         <v>-7</v>
@@ -11002,7 +11002,7 @@
         <v>17.00204466013176</v>
       </c>
       <c r="H39" t="n">
-        <v>18.95418253970968</v>
+        <v>18.93002705952216</v>
       </c>
       <c r="I39" t="n">
         <v>12</v>
@@ -11044,7 +11044,7 @@
         <v>-1.482522629252884</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.468971684960422</v>
+        <v>-1.469126908495525</v>
       </c>
       <c r="I40" t="n">
         <v>-7</v>
@@ -11086,10 +11086,10 @@
         <v>11.49666284258683</v>
       </c>
       <c r="H41" t="n">
-        <v>12.37126026294425</v>
+        <v>12.36063344970265</v>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J41" t="n">
         <v>0.720931701455477</v>
@@ -11128,7 +11128,7 @@
         <v>2.51027743909188</v>
       </c>
       <c r="H42" t="n">
-        <v>2.550119478968952</v>
+        <v>2.549653560848185</v>
       </c>
       <c r="I42" t="n">
         <v>2</v>
@@ -11170,10 +11170,10 @@
         <v>-6.35872594168498</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.117999683787076</v>
+        <v>-6.120679461215559</v>
       </c>
       <c r="I43" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="J43" t="n">
         <v>-1.304442875892249</v>
@@ -11212,7 +11212,7 @@
         <v>2.478555525865715</v>
       </c>
       <c r="H44" t="n">
-        <v>2.517389678850918</v>
+        <v>2.516935617491924</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -11254,7 +11254,7 @@
         <v>-2.85805659644484</v>
       </c>
       <c r="H45" t="n">
-        <v>-2.808164543107154</v>
+        <v>-2.808731674178404</v>
       </c>
       <c r="I45" t="n">
         <v>-7</v>
@@ -11296,7 +11296,7 @@
         <v>-0.2984681229394823</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.2979145891790438</v>
+        <v>-0.2979209703863148</v>
       </c>
       <c r="I46" t="n">
         <v>-7</v>
@@ -11338,7 +11338,7 @@
         <v>0.1267217221991075</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1268217764904591</v>
+        <v>0.1268206204660771</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -11380,7 +11380,7 @@
         <v>-0.022546233969166</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.02254306974532483</v>
+        <v>-0.02254310627608902</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -11422,7 +11422,7 @@
         <v>-0.5291477727514575</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.5274105613365236</v>
+        <v>-0.5274305635861367</v>
       </c>
       <c r="I49" t="n">
         <v>-7</v>
@@ -11464,7 +11464,7 @@
         <v>0.1322806095846829</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1323896384166403</v>
+        <v>0.1323883786639897</v>
       </c>
       <c r="I50" t="n">
         <v>2</v>
@@ -11506,7 +11506,7 @@
         <v>-13.75172919627062</v>
       </c>
       <c r="H51" t="n">
-        <v>-12.69368177963798</v>
+        <v>-12.70487422236903</v>
       </c>
       <c r="I51" t="n">
         <v>-16</v>
@@ -11548,7 +11548,7 @@
         <v>-1.789888346342963</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.770176756235884</v>
+        <v>-1.770402167313677</v>
       </c>
       <c r="I52" t="n">
         <v>-7</v>
@@ -11590,7 +11590,7 @@
         <v>3.93308417153446</v>
       </c>
       <c r="H53" t="n">
-        <v>4.031698040814206</v>
+        <v>4.03053696283564</v>
       </c>
       <c r="I53" t="n">
         <v>2</v>
@@ -11632,7 +11632,7 @@
         <v>2.362687237685464</v>
       </c>
       <c r="H54" t="n">
-        <v>2.397951132692526</v>
+        <v>2.397539049856874</v>
       </c>
       <c r="I54" t="n">
         <v>2</v>
@@ -11674,7 +11674,7 @@
         <v>-3.755102987488499</v>
       </c>
       <c r="H55" t="n">
-        <v>-3.669519942750981</v>
+        <v>-3.670487764091916</v>
       </c>
       <c r="I55" t="n">
         <v>-8</v>
@@ -11716,7 +11716,7 @@
         <v>-11.57055422688154</v>
       </c>
       <c r="H56" t="n">
-        <v>-240.7845567739307</v>
+        <v>-241.0562922685989</v>
       </c>
       <c r="I56" t="n">
         <v>-232</v>
@@ -11758,7 +11758,7 @@
         <v>13.7202155022602</v>
       </c>
       <c r="H57" t="n">
-        <v>194.2154432260691</v>
+        <v>193.9437077314009</v>
       </c>
       <c r="I57" t="n">
         <v>203</v>
@@ -11800,7 +11800,7 @@
         <v>6.438228190001382</v>
       </c>
       <c r="H58" t="n">
-        <v>194.2154432260691</v>
+        <v>193.9437077314009</v>
       </c>
       <c r="I58" t="n">
         <v>203</v>
@@ -11842,7 +11842,7 @@
         <v>-26.41907006064213</v>
       </c>
       <c r="H59" t="n">
-        <v>-240.7845567739307</v>
+        <v>-241.0562922685989</v>
       </c>
       <c r="I59" t="n">
         <v>-232</v>
@@ -11884,7 +11884,7 @@
         <v>16.65163839286495</v>
       </c>
       <c r="H60" t="n">
-        <v>18.52203146202419</v>
+        <v>18.49891169079245</v>
       </c>
       <c r="I60" t="n">
         <v>12</v>
@@ -11926,7 +11926,7 @@
         <v>-38.02374244188189</v>
       </c>
       <c r="H61" t="n">
-        <v>-31.98100979762563</v>
+        <v>-32.03038238463745</v>
       </c>
       <c r="I61" t="n">
         <v>-20</v>
@@ -11968,10 +11968,10 @@
         <v>-10.44373543847883</v>
       </c>
       <c r="H62" t="n">
-        <v>-9.815410196102391</v>
+        <v>-9.822218581899108</v>
       </c>
       <c r="I62" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="J62" t="n">
         <v>-2.959683285858944</v>
@@ -12010,7 +12010,7 @@
         <v>16.52047361559173</v>
       </c>
       <c r="H63" t="n">
-        <v>18.36072952635908</v>
+        <v>18.33799127604846</v>
       </c>
       <c r="I63" t="n">
         <v>12</v>
@@ -12245,25 +12245,25 @@
         <v>49.95866382933372</v>
       </c>
       <c r="K2" t="n">
-        <v>240.7845567739309</v>
+        <v>241.0562922685991</v>
       </c>
       <c r="L2" t="n">
         <v>232</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003159383068485067</v>
+        <v>0.0003146284570458846</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9999999903295805</v>
+        <v>0.9999999904157906</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P2" t="n">
         <v>232</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R2" t="n">
         <v>49.47003071465429</v>
@@ -12335,25 +12335,25 @@
         <v>47.4566775584923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002444538359925252</v>
+        <v>0.0024456321524845</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>8.992806499463768e-15</v>
+        <v>8.770761894538737e-15</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0008424094662410342</v>
+        <v>0.0008430654729580378</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1082949702883258</v>
+        <v>0.108408644246943</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R3" t="n">
         <v>34</v>
@@ -12392,7 +12392,7 @@
         <v>-22.01090870820175</v>
       </c>
       <c r="AD3" t="n">
-        <v>-240.782112235571</v>
+        <v>-241.0538466364466</v>
       </c>
       <c r="AE3" t="n">
         <v>-232</v>
@@ -12441,25 +12441,25 @@
         <v>51.4375944933018</v>
       </c>
       <c r="K4" t="n">
-        <v>434.9999964909729</v>
+        <v>434.9999965808095</v>
       </c>
       <c r="L4" t="n">
         <v>435</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9999993231823747</v>
+        <v>0.9999993394351745</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999986</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9082949702883258</v>
+        <v>0.908408644246943</v>
       </c>
       <c r="P4" t="n">
         <v>435</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R4" t="n">
         <v>68.99999996553919</v>
@@ -12498,7 +12498,7 @@
         <v>11.08667231966635</v>
       </c>
       <c r="AD4" t="n">
-        <v>194.215439717042</v>
+        <v>193.9437043122104</v>
       </c>
       <c r="AE4" t="n">
         <v>203</v>
@@ -12547,25 +12547,25 @@
         <v>44.3832216650333</v>
       </c>
       <c r="K5" t="n">
-        <v>217.9164721422565</v>
+        <v>218.1562549826575</v>
       </c>
       <c r="L5" t="n">
         <v>213</v>
       </c>
       <c r="M5" t="n">
-        <v>2.476778858684359e-05</v>
+        <v>2.48155853487253e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.999999678009311</v>
+        <v>0.9999996831718609</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P5" t="n">
         <v>232</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R5" t="n">
         <v>43.74181580550341</v>
@@ -12604,7 +12604,7 @@
         <v>-26.24558139227108</v>
       </c>
       <c r="AD5" t="n">
-        <v>-22.86808463167438</v>
+        <v>-22.90003728594155</v>
       </c>
       <c r="AE5" t="n">
         <v>-19</v>
@@ -12653,25 +12653,25 @@
         <v>51.4925577142842</v>
       </c>
       <c r="K6" t="n">
-        <v>233.046174363298</v>
+        <v>233.3136421095338</v>
       </c>
       <c r="L6" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0001497193455752832</v>
+        <v>0.000149349159720813</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9999999701271129</v>
+        <v>0.9999999704655971</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P6" t="n">
         <v>232</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R6" t="n">
         <v>50.97031206440118</v>
@@ -12710,10 +12710,10 @@
         <v>-8.126120881705049</v>
       </c>
       <c r="AD6" t="n">
-        <v>-7.738382410632937</v>
+        <v>-7.742650159065278</v>
       </c>
       <c r="AE6" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AF6" t="n">
         <v>1.53389388495048</v>
@@ -12759,25 +12759,25 @@
         <v>51.16875448388685</v>
       </c>
       <c r="K7" t="n">
-        <v>248.1983577747174</v>
+        <v>248.466203805787</v>
       </c>
       <c r="L7" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0005880033471709067</v>
+        <v>0.0005847952418970292</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9999999964955052</v>
+        <v>0.9999999965188102</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P7" t="n">
         <v>232</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R7" t="n">
         <v>50.6595822788417</v>
@@ -12816,10 +12816,10 @@
         <v>7.088073730799863</v>
       </c>
       <c r="AD7" t="n">
-        <v>7.41380100078652</v>
+        <v>7.409911537187952</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>1.210090654553127</v>
@@ -12865,25 +12865,25 @@
         <v>49.0784251211193</v>
       </c>
       <c r="K8" t="n">
-        <v>235.5445294262944</v>
+        <v>235.8142955576552</v>
       </c>
       <c r="L8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0001928573207014561</v>
+        <v>0.0001922688882681767</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9999999794054031</v>
+        <v>0.9999999796226009</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P8" t="n">
         <v>232</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R8" t="n">
         <v>48.58056426133453</v>
@@ -12922,10 +12922,10 @@
         <v>-5.415909265881339</v>
       </c>
       <c r="AD8" t="n">
-        <v>-5.240027347636499</v>
+        <v>-5.241996710943852</v>
       </c>
       <c r="AE8" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="AF8" t="n">
         <v>-0.8802387082144278</v>
@@ -12971,25 +12971,25 @@
         <v>53.07426709491409</v>
       </c>
       <c r="K9" t="n">
-        <v>255.8265858199104</v>
+        <v>256.0828019608846</v>
       </c>
       <c r="L9" t="n">
         <v>242</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00102976501607499</v>
+        <v>0.001023004016304174</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9999999986903431</v>
+        <v>0.9999999986960765</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P9" t="n">
         <v>232</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R9" t="n">
         <v>52.43732072789154</v>
@@ -13028,7 +13028,7 @@
         <v>13.77494885159695</v>
       </c>
       <c r="AD9" t="n">
-        <v>15.04202904597955</v>
+        <v>15.02650969228552</v>
       </c>
       <c r="AE9" t="n">
         <v>10</v>
@@ -13077,25 +13077,25 @@
         <v>45.8851159430974</v>
       </c>
       <c r="K10" t="n">
-        <v>213.6871807016408</v>
+        <v>213.9180360202207</v>
       </c>
       <c r="L10" t="n">
         <v>213</v>
       </c>
       <c r="M10" t="n">
-        <v>1.390487849217692e-05</v>
+        <v>1.395267390913446e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9999993658165374</v>
+        <v>0.9999993767653692</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P10" t="n">
         <v>232</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R10" t="n">
         <v>45.27357467477539</v>
@@ -13134,7 +13134,7 @@
         <v>-31.69305534396889</v>
       </c>
       <c r="AD10" t="n">
-        <v>-27.0973760722901</v>
+        <v>-27.13825624837838</v>
       </c>
       <c r="AE10" t="n">
         <v>-19</v>
@@ -13183,25 +13183,25 @@
         <v>50.91154436634739</v>
       </c>
       <c r="K11" t="n">
-        <v>264.237212036493</v>
+        <v>264.4728881880322</v>
       </c>
       <c r="L11" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001773768855661051</v>
+        <v>0.001760343699477196</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9999999995307245</v>
+        <v>0.999999999531632</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P11" t="n">
         <v>232</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R11" t="n">
         <v>50.41037501016341</v>
@@ -13240,10 +13240,10 @@
         <v>20.56692826905112</v>
       </c>
       <c r="AD11" t="n">
-        <v>23.45265526256213</v>
+        <v>23.41659591943318</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
         <v>0.9528805370136695</v>
@@ -13289,25 +13289,25 @@
         <v>49.78768851662465</v>
       </c>
       <c r="K12" t="n">
-        <v>234.7056389213595</v>
+        <v>234.9747285289677</v>
       </c>
       <c r="L12" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0001773760685311876</v>
+        <v>0.0001768685710000217</v>
       </c>
       <c r="N12" t="n">
-        <v>0.9999999766850866</v>
+        <v>0.9999999769371066</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5476108299062733</v>
+        <v>0.5477245038648905</v>
       </c>
       <c r="P12" t="n">
         <v>232</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R12" t="n">
         <v>49.29868383300175</v>
@@ -13346,10 +13346,10 @@
         <v>-6.316537033636223</v>
       </c>
       <c r="AD12" t="n">
-        <v>-6.078917852571408</v>
+        <v>-6.081563739631378</v>
       </c>
       <c r="AE12" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="AF12" t="n">
         <v>-0.170975312709075</v>
@@ -13541,25 +13541,25 @@
         <v>47.4566775584923</v>
       </c>
       <c r="K2" t="n">
-        <v>0.002444538359925252</v>
+        <v>0.0024456321524845</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>8.992806499463768e-15</v>
+        <v>8.770761894538737e-15</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0008424094662410342</v>
+        <v>0.0008430654729580378</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1082949702883258</v>
+        <v>0.108408644246943</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R2" t="n">
         <v>34</v>
@@ -13623,25 +13623,25 @@
         <v>48.06309849694068</v>
       </c>
       <c r="K3" t="n">
-        <v>3.800774445190354</v>
+        <v>3.797937367292421</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1.075362021651927e-12</v>
+        <v>1.054545339940205e-12</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5139424949687793</v>
+        <v>0.5138444111769637</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2082949702883258</v>
+        <v>0.2084086442469429</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R3" t="n">
         <v>34.00000000006854</v>
@@ -13705,25 +13705,25 @@
         <v>48.6769738659123</v>
       </c>
       <c r="K4" t="n">
-        <v>46.36030590120986</v>
+        <v>46.33217046998966</v>
       </c>
       <c r="L4" t="n">
         <v>33</v>
       </c>
       <c r="M4" t="n">
-        <v>2.416989386411217e-10</v>
+        <v>2.381260744144242e-10</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9894248965063919</v>
+        <v>0.9894245958623763</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3082949702883258</v>
+        <v>0.308408644246943</v>
       </c>
       <c r="P4" t="n">
         <v>33</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R4" t="n">
         <v>34.00019624383491</v>
@@ -13787,25 +13787,25 @@
         <v>49.29905765753127</v>
       </c>
       <c r="K5" t="n">
-        <v>146.6832458223741</v>
+        <v>146.6698172062344</v>
       </c>
       <c r="L5" t="n">
         <v>159</v>
       </c>
       <c r="M5" t="n">
-        <v>8.622835284688435e-08</v>
+        <v>8.534592926823237e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9999641538790984</v>
+        <v>0.9999642370916015</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4082949702883258</v>
+        <v>0.408408644246943</v>
       </c>
       <c r="P5" t="n">
         <v>159</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R5" t="n">
         <v>34.40516195819973</v>
@@ -13869,25 +13869,25 @@
         <v>49.86416595433454</v>
       </c>
       <c r="K6" t="n">
-        <v>216.2729051455449</v>
+        <v>216.4425791995704</v>
       </c>
       <c r="L6" t="n">
         <v>213</v>
       </c>
       <c r="M6" t="n">
-        <v>3.375684386919264e-05</v>
+        <v>3.35610808149811e-05</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9999999084346971</v>
+        <v>0.9999999090537282</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5082949702883257</v>
+        <v>0.5084086442469429</v>
       </c>
       <c r="P6" t="n">
         <v>213</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R6" t="n">
         <v>42.46929620834526</v>
@@ -13951,25 +13951,25 @@
         <v>50.26602529121147</v>
       </c>
       <c r="K7" t="n">
-        <v>299.9041175515985</v>
+        <v>300.2042211040786</v>
       </c>
       <c r="L7" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M7" t="n">
-        <v>0.007321739761032842</v>
+        <v>0.00730824562759147</v>
       </c>
       <c r="N7" t="n">
-        <v>0.9999999996373282</v>
+        <v>0.9999999996418719</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6082949702883256</v>
+        <v>0.6084086442469429</v>
       </c>
       <c r="P7" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R7" t="n">
         <v>58.30588642669247</v>
@@ -14033,25 +14033,25 @@
         <v>50.64945766609645</v>
       </c>
       <c r="K8" t="n">
-        <v>410.8184878131538</v>
+        <v>410.8858017641114</v>
       </c>
       <c r="L8" t="n">
         <v>429</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3003351780998192</v>
+        <v>0.3004790411151449</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9999999999971318</v>
+        <v>0.9999999999971859</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7082949702883258</v>
+        <v>0.7084086442469428</v>
       </c>
       <c r="P8" t="n">
         <v>429</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R8" t="n">
         <v>68.28958904277034</v>
@@ -14115,25 +14115,25 @@
         <v>51.04262162117158</v>
       </c>
       <c r="K9" t="n">
-        <v>434.7544019966205</v>
+        <v>434.756134058466</v>
       </c>
       <c r="L9" t="n">
         <v>435</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9685761775298323</v>
+        <v>0.968725726654492</v>
       </c>
       <c r="N9" t="n">
-        <v>0.999999999999953</v>
+        <v>0.9999999999999543</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8082949702883258</v>
+        <v>0.808408644246943</v>
       </c>
       <c r="P9" t="n">
         <v>435</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R9" t="n">
         <v>68.99876747283841</v>
@@ -14197,25 +14197,25 @@
         <v>51.4375944933018</v>
       </c>
       <c r="K10" t="n">
-        <v>434.9999964909729</v>
+        <v>434.9999965808095</v>
       </c>
       <c r="L10" t="n">
         <v>435</v>
       </c>
       <c r="M10" t="n">
-        <v>0.9999993231823747</v>
+        <v>0.9999993394351745</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9999999999999984</v>
+        <v>0.9999999999999986</v>
       </c>
       <c r="O10" t="n">
-        <v>0.9082949702883258</v>
+        <v>0.908408644246943</v>
       </c>
       <c r="P10" t="n">
         <v>435</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.17479560915943</v>
+        <v>12.16881140592611</v>
       </c>
       <c r="R10" t="n">
         <v>68.99999996553919</v>
@@ -15291,7 +15291,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0.03334357615565864</v>
+        <v>0.03334349623901289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02136918271787636</v>
+        <v>0.02136914989375782</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
